--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D5-LOCAL-20260726T101447Z</t>
+          <t>D5-LOCAL-20260727T034533Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -519,7 +519,7 @@
         <v>529</v>
       </c>
       <c r="H2" t="n">
-        <v>141.9824172999943</v>
+        <v>399.6533368999371</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19104</v>
+        <v>19291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2c2c2c9844e808710c04a437e2306c587d402ff058be130254cfe4def7a5d5c0</t>
+          <t>f8312bd715f08bc9d5dea8ed8434c98bfbec71ab9530ef9d8d90120e4a96e4e9</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2d413864a92b055daec6186f656be274ec50c484561e3210399c5c6b1f446315</t>
+          <t>fc246996bdcd0f15017212655ad35b72dd7d96e4eec43bcb9e5fea9f3957e8fb</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>37c14424a5530521a5067e23003d3bc1979fea3f4a8b1542699d2da93b145ea8</t>
+          <t>f0eedac9032660fbe17b8b9920fac72b186e2f9dc6b9c9405971db86a5fab765</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c2afb9111cef19a762c6cb7f4b3122d5f1825deddcf9536186c3db1fcca09e29</t>
+          <t>c65b91c67204e259a7c69f7fa760ed18017143c981aa65d3d711734b7f168256</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>e59bb38e1bb0a1f04c26de29e32107a46493ec1f6d65afad2c2fe8a35408f06e</t>
+          <t>0ff7bc8adfe746a36eed9918ad7dcb156931da693572c68482d72f23e425b1fd</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>a92de767a031fcdfb9738f850d7c5e2fb204f0fff590d7115684e11efde6442f</t>
+          <t>eb960d8681066aa531c701f2ff8263c6fa7a91827df14cd5f802fc4f0e939cb1</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>f674fe536f33d604c8a43db63d9e16bc736dfd1fe7d3637459182d00613aff47</t>
+          <t>39035906df9ec1fded81b3728bc798020fc86a26ae5c1125ac53b672aec31b28</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7188eab11a4f84c80601e112cb1b922435b9fae31f40bfff6104a407415740ee</t>
+          <t>b85a30747a01feea43c0171e06a3a5e5635443a0d3fbb6480a475fb591398f2b</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>d4dccc240e0f8c6b6c88c2b72bfb70c27573a001eb1eabf34e429249e3c212cd</t>
+          <t>fc1f2df5573cd42cd08b5f3f3d5aab65d7481385b8dd4eb1655560849ef4d8e6</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>b37cf4f6155db1f64ec732949ab9490409a6d4ebfceb9b070662db2c769155d2</t>
+          <t>f6aad9dd6cfc331d694132112f20a51de8e1177c270cd4bbb7f166281963bdbd</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>981a2e837237b5b4eaee195e059038b1553d2f7f50f740db8c2d477533287f95</t>
+          <t>2a6543ea258e75300624e9b9e292350510aa2c351d173bbed3c3ff51569919c5</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>b6e4e1b963fd762979980185eebfd958d998c277f90e96ea132428abe6629d07</t>
+          <t>412b09b568ea6bf9ea98c120a8d4810ffcc4b9c60e282d59e60a304ad64ff4aa</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4ea723971448a414cd9b37459a986ace70298ca97338c6de56afff271ea19419</t>
+          <t>f66cad2e02e6058e23ea1544558bff89c71b6297c805d30db5ec408194382e61</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6135</v>
+        <v>6136</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>25958fe3b582dd85a830e86c75ac518d8d11ef34b4ce5543fc5d4f0592672f79</t>
+          <t>c0bf0a9d4bb4b4a04ba10325b945884fc3ff9dbe2563db65c2e85bf2f03305eb</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72551</v>
+        <v>72624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>f8ac0bd01788395a92e25311325280b4ef3b3638363f53335e517f1d8b893955</t>
+          <t>a779a4aeac4c82bd4ee1f1ea1f2ba9b0fd8f079a0217ff521ac640680ffa70f2</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1536,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>44211</v>
+        <v>44198</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>37871dde3a4f2bcf4ab5c0002f11bb991176d03b2dcdd18358167c558104fc28</t>
+          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26856</v>
+        <v>26857</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>92560070976d2e570f958a05dbc99e5a593675b582d9d19a4d87ab0df6e9e277</t>
+          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7156b2e4ebefca903880838e48f3fa34fbeb43ace78300204b2ff06559342bff</t>
+          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
         </is>
       </c>
     </row>
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>140058</v>
+        <v>140097</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>792759410b1da514ab6619bfab82eaf960ced9c499e8812a1cde60801c4170ac</t>
+          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>51c9562e1a803efcdf280d46251b2b88007e26e99072a8e7e9b0f8f5df107f3c</t>
+          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
         </is>
       </c>
     </row>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5205699</v>
+        <v>5209422</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>08278f5c57cf5348b2eab333b71e90d97e61112162f23476b34cc5552bada51e</t>
+          <t>855000b4c1c9baeb5b01080b5c15e7cff136b3499918ebaa56035930805b5317</t>
         </is>
       </c>
     </row>
@@ -1641,11 +1641,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7340516</v>
+        <v>7340495</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20583506fa499922f7b4bffc01a8bd4e938d3e70d8a9cf48ad151d8290caf64e</t>
+          <t>ecbeb02c2c1285846d4f9f0b88dbf278da1a0c194d46124a736a2665356893ad</t>
         </is>
       </c>
     </row>
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>45296304</v>
+        <v>45254824</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ba658837f7d0b538805371cf0ce656b71fbcfeac43a9d232499c9a1174e54467</t>
+          <t>b46196c533474ef2a2e56b661e33def9928911b3e90ac7b6fb6e098200c88c34</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20240</v>
+        <v>20237</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>d21d3eb558c3039b7b89619e5270c93a3df59f820b149e7db7aec1c907fa15de</t>
+          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>cc5181497039d0420b5eb2f1c77b74c14df13ed37b6b3d8a7225b6548ce6cbbc</t>
+          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
         </is>
       </c>
     </row>
@@ -1716,11 +1716,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>228948</v>
+        <v>228952</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2211c1beae4997736c4614f6899e8cb8ca8cecf27516279a904bbada6c14ec28</t>
+          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
         </is>
       </c>
     </row>
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3658909</v>
+        <v>3658910</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>f60ae3b03aea47be2eed825c2f8b4ed1697a8095fc65ded01fd391568af3dce3</t>
+          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
         </is>
       </c>
     </row>
@@ -1746,11 +1746,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45835271</v>
+        <v>45834835</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>79a2b9c4441b2ef9a4d7b625e2e4ce8c09a0d56ba1220a02ebda8094a7d82300</t>
+          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1761,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1171213</v>
+        <v>1171194</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0b8a69770a20b73fa282844da9b61ec47ad8d10b2dc8aab5722586dda154079c</t>
+          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
         </is>
       </c>
     </row>
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>11405236</v>
+        <v>11410677</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>70d639d2f947e9ff9062c6f47aa9c334c435065694eb9f9b7078408c31ee900d</t>
+          <t>5202013a113539fedcbf11f84847bed164f512b380c978712e8cd60767d2a8ed</t>
         </is>
       </c>
     </row>
@@ -1806,11 +1806,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6011211</v>
+        <v>6011187</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>30f5454a361fe57ada933909c386ea230b87a71df728326740d4bc3d436fade1</t>
+          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
         </is>
       </c>
     </row>
@@ -1821,11 +1821,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16402886</v>
+        <v>16403976</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5a2a6477a525d0129acca5d5ac5a9a212d65b8971c558163bad439bc7e5d2772</t>
+          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
         </is>
       </c>
     </row>
@@ -1836,11 +1836,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7443</v>
+        <v>7442</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>af9c2b738699995183017bdca24ecf7079d8e3d626de045ef913015ddfb2bc7f</t>
+          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>51d0841f29d5cff2b6e76247be9c1f8b909f1663bbbae99cebd322a83ae61dcd</t>
+          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
         </is>
       </c>
     </row>
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15963797</v>
+        <v>15958642</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cd5fc3d47cb5a99adb3e245ec696fec421ff097eed699f22c9710305dcc1b3cb</t>
+          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>a9c74e8ea0fe575ecd9b5686e5f7cff0073d4f8eacb905123ee04be5419b4b3b</t>
+          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
         </is>
       </c>
     </row>
@@ -1896,11 +1896,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>190697</v>
+        <v>190694</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>e2b1e4d2c76ba6fea16efdd38b58750e49042f07566fa70e84a56df664694916</t>
+          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
         </is>
       </c>
     </row>
@@ -1911,11 +1911,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52816</v>
+        <v>52815</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>b22306d605a8c8b90683c085300b1ea26b0ef0ebfdf7b28ccf64e46a7b94977f</t>
+          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
         </is>
       </c>
     </row>
@@ -1926,11 +1926,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28020</v>
+        <v>28033</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5489e9a48b31794d8d7622ac093e6532807f3536715a1b911b5f124e70290693</t>
+          <t>b4afe3b108022b10467766365ef33146cc1991c2778350c1dc7bd2c6ad146dc4</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9dac94245e51fcfcba9b6a066453c8e99e98dd57d1fd9c0ff08659cf9880308c</t>
+          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
         </is>
       </c>
     </row>
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9971</v>
+        <v>9964</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>499a0b87c3e85af5ba09bb8e70ee30d911794d12e4c4b8962910e46bdb204927</t>
+          <t>d053b19a1d7f2a6c50f4080a33698ddaa465ad7c829d943a416bc73fd8f862dd</t>
         </is>
       </c>
     </row>
@@ -1971,11 +1971,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1780</v>
+        <v>2342</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>c5459512330f653905aa18ac1ae64e49d5fa7910302f64c121aa9a6881b0d533</t>
+          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
         </is>
       </c>
     </row>
@@ -1986,11 +1986,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14108</v>
+        <v>14821</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>20deef6c6f6d8f1bf1de5db6e69ee3aa6b7cfcde1b41612c7a4128c2575b18b2</t>
+          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
         </is>
       </c>
     </row>
@@ -2016,11 +2016,11 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11668</v>
+        <v>11679</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>967cf5faa35615123511022ff1a089d7e2b73592f5c0fc1b827ca9f1cb3de244</t>
+          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
         </is>
       </c>
     </row>
@@ -2031,11 +2031,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2817</v>
+        <v>2838</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1791ed3baee481c51316bc61f172d3c0dd5f48af1fcd2c6d8dbda0d47250a722</t>
+          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
         </is>
       </c>
     </row>
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>60796</v>
+        <v>60791</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2d5d34273b92475f6cc718758d2cd1d02d604721043ae664140b92c1e7a5b6c6</t>
+          <t>cf67d0299512e1a849e6b4115b54905061a8ec408d060765725086af8eadeea3</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>d7492b5968dc2535d7a84a6a6bf0b6bb31e1543c641e3db58bae3ef89c85dc4b</t>
+          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
         </is>
       </c>
     </row>
@@ -2076,11 +2076,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7272601</v>
+        <v>7277839</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>95d0f1c5333968ceb35e986b108bc66065a71ecb8d33d1457ed494f09b8f4f05</t>
+          <t>659954b3407793180cb551f9e453f5700c00fe00e8e35d9d30156360bec78c54</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>059d35b163c8b5a79c31c926b50ed2a72dc5a3ecff3bba5b135913e3c77f066c</t>
+          <t>9a09febd2f64c3daebfbc6497f33ee99932a03ee2d99c76474870b5d8e758d3b</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>f2ded76629b30e73676c6c7c4cba68d91e231fe5a24d849777ce51a9ca414040</t>
+          <t>3228e392670b6b7e4cf4ae59ca73c9cc30a9f39deb7ed61d4c2b5b30148a9431</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5208c9594d7e0733c9538bd09d494cd868ac7141909c7f8592721d79ee51afea</t>
+          <t>6b74bdce8143126cd56e229752140572345a8928aedb16d74f0f43e4a814a33f</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6287a00475c1ac65a4a8142f26b942203007feb00a35693a39fb4b7b36a26115</t>
+          <t>70a6002a470981c1845fdb8b6515c4c161422b921f9aafa149ece58f1fbc93fd</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ae8ced78da84ae17220dc3c9f67418c593ac8e9ff0edce252c636a908b5e9e44</t>
+          <t>5dff072b15712c666dead3dd588629745b7d2556ed97f2a56253d65de236552d</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>327b7067add6ba182e382b2d92295a1beb03985efbb405b445633408ccedeb4d</t>
+          <t>b39443cff99b1acc69cd752c93e0a4a56f4f86f0663715b7ba958aa9987a75bd</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>a0c2bce69890a23091634e2a574ac19b1581ee5aad1f4d754432744d10abd66b</t>
+          <t>1123afd60f847e11c0bf2485aafea5afbcf5010457413fd4d30ceb7df6f4eba8</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>e769f070368d3f74a9bea4545401820b1a7565ff756f7fd888c19366b3f55945</t>
+          <t>f829df37d53ad5209dc4a49064a5f3b29494e00f08b1c23b8604e12280e4ef81</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>b8b6f682439762fe36c20830c800b697b94f5653c8014363fff2880afabc1c05</t>
+          <t>ffe2846ce2e6b715e433d9d3dee91a8226d705708caa8dee900435aa21c70647</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>e1ba81b161bbf531ba8bd193bd527945a693174fd8292e80f4adb555a65068ff</t>
+          <t>592082fa5efa9958cb1d42843c7829c0472ffea2ce98c226e47077952e9ebac2</t>
         </is>
       </c>
     </row>
@@ -2421,11 +2421,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>9998183</v>
+        <v>10003889</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>a50c85c851a23c40244b0013f3cbdb7173eb41dfe87a692a3b0c2327d68633f0</t>
+          <t>e83b7c789dc587697a193958b2b6b56b5d7a3726b536f9692aaff0aa1b53a61e</t>
         </is>
       </c>
     </row>
@@ -2436,11 +2436,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>41680</v>
+        <v>41681</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3e3c1921076db202eaecb1f48cbc785f841cc4df5360a80802b08d3df3d007b6</t>
+          <t>934e1de7cff35a729cedb7cc394c1586ab8448a646598fe18c94f6c61dd7c29b</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14538</v>
+        <v>14539</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>6fc687ee00c730debc22deae82216a5ef3bbd6040f20006ee3e9a4fe4517ce90</t>
+          <t>b897bc68bcc66c202993c56c1700d80696ef344dd91d28f1709d1a3bf7a9e511</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>b5ad82eea95ba96c948599521079351102e115a7f6d6654edae12407413a0908</t>
+          <t>f0d0f525653abcdfe59df31be1600ad5c48cb7bc49fc7291b413add17243748d</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2be5fed42543594038bcbd521d2ba1f67c4d2b387c000c15e2dd0af351bcbf94</t>
+          <t>718330455f0b28a855c37e00242b9ce531f16bc9c55f3856bd9ae50c183789e9</t>
         </is>
       </c>
     </row>
@@ -2659,14 +2659,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2817</v>
+        <v>2838</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>46229.36366268519</v>
+        <v>46230.15591561342</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1791ed3baee481c51316bc61f172d3c0dd5f48af1fcd2c6d8dbda0d47250a722</t>
+          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -2688,14 +2688,14 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1780</v>
+        <v>2342</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>46229.36366268519</v>
+        <v>46230.15588011574</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>c5459512330f653905aa18ac1ae64e49d5fa7910302f64c121aa9a6881b0d533</t>
+          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G16" t="n">
         <v>30</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G17" t="n">
         <v>30</v>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G18" t="n">
         <v>30</v>
@@ -3470,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G19" t="n">
         <v>30</v>
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G20" t="n">
         <v>30</v>
@@ -3540,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G21" t="n">
         <v>30</v>
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G22" t="n">
         <v>30</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G23" t="n">
         <v>30</v>
@@ -3645,7 +3645,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G24" t="n">
         <v>30</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G25" t="n">
         <v>30</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G26" t="n">
         <v>30</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G27" t="n">
         <v>30</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G28" t="n">
         <v>30</v>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5827791039015304</v>
+        <v>0.5827791039015302</v>
       </c>
       <c r="G29" t="n">
         <v>30</v>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G58" t="n">
         <v>30</v>
@@ -4870,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G59" t="n">
         <v>30</v>
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G60" t="n">
         <v>30</v>
@@ -4940,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G61" t="n">
         <v>30</v>
@@ -4975,7 +4975,7 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G62" t="n">
         <v>30</v>
@@ -5010,7 +5010,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G63" t="n">
         <v>30</v>
@@ -5045,7 +5045,7 @@
         <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G64" t="n">
         <v>30</v>
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G65" t="n">
         <v>30</v>
@@ -5115,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G66" t="n">
         <v>30</v>
@@ -5150,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G67" t="n">
         <v>30</v>
@@ -5185,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G68" t="n">
         <v>30</v>
@@ -5220,7 +5220,7 @@
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G69" t="n">
         <v>30</v>
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G70" t="n">
         <v>30</v>
@@ -5290,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4847581538360896</v>
+        <v>0.4847581538360898</v>
       </c>
       <c r="G71" t="n">
         <v>30</v>
@@ -5325,7 +5325,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G72" t="n">
         <v>30</v>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G73" t="n">
         <v>30</v>
@@ -5395,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G74" t="n">
         <v>30</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G75" t="n">
         <v>30</v>
@@ -5465,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G76" t="n">
         <v>30</v>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G77" t="n">
         <v>30</v>
@@ -5535,7 +5535,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G78" t="n">
         <v>30</v>
@@ -5570,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G79" t="n">
         <v>30</v>
@@ -5605,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G80" t="n">
         <v>30</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G81" t="n">
         <v>30</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G82" t="n">
         <v>30</v>
@@ -5710,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G83" t="n">
         <v>30</v>
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G84" t="n">
         <v>30</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8644974417792134</v>
+        <v>0.8644974417792132</v>
       </c>
       <c r="G85" t="n">
         <v>30</v>
@@ -5815,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G86" t="n">
         <v>30</v>
@@ -5850,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G87" t="n">
         <v>30</v>
@@ -5885,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G88" t="n">
         <v>30</v>
@@ -5920,7 +5920,7 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G89" t="n">
         <v>30</v>
@@ -5955,7 +5955,7 @@
         <v>1</v>
       </c>
       <c r="F90" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G90" t="n">
         <v>30</v>
@@ -5990,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G91" t="n">
         <v>30</v>
@@ -6025,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G92" t="n">
         <v>30</v>
@@ -6060,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G93" t="n">
         <v>30</v>
@@ -6095,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G94" t="n">
         <v>30</v>
@@ -6130,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G95" t="n">
         <v>30</v>
@@ -6165,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G96" t="n">
         <v>30</v>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G97" t="n">
         <v>30</v>
@@ -6235,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G98" t="n">
         <v>30</v>
@@ -6270,7 +6270,7 @@
         <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>0.552698716802185</v>
+        <v>0.5526987168021851</v>
       </c>
       <c r="G99" t="n">
         <v>30</v>
@@ -6305,7 +6305,7 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G100" t="n">
         <v>30</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G101" t="n">
         <v>30</v>
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G102" t="n">
         <v>30</v>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G103" t="n">
         <v>30</v>
@@ -6445,7 +6445,7 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G104" t="n">
         <v>30</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G105" t="n">
         <v>30</v>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G106" t="n">
         <v>30</v>
@@ -6550,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G107" t="n">
         <v>30</v>
@@ -6585,7 +6585,7 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G108" t="n">
         <v>30</v>
@@ -6620,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G109" t="n">
         <v>30</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G110" t="n">
         <v>30</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G111" t="n">
         <v>30</v>
@@ -6725,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G112" t="n">
         <v>30</v>
@@ -6760,7 +6760,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.449341287860834</v>
+        <v>0.4493412878608337</v>
       </c>
       <c r="G113" t="n">
         <v>30</v>
@@ -6795,7 +6795,7 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G114" t="n">
         <v>30</v>
@@ -6830,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G115" t="n">
         <v>30</v>
@@ -6865,7 +6865,7 @@
         <v>1</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G116" t="n">
         <v>30</v>
@@ -6900,7 +6900,7 @@
         <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G117" t="n">
         <v>30</v>
@@ -6935,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G118" t="n">
         <v>30</v>
@@ -6970,7 +6970,7 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G119" t="n">
         <v>30</v>
@@ -7005,7 +7005,7 @@
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G120" t="n">
         <v>30</v>
@@ -7040,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G121" t="n">
         <v>30</v>
@@ -7075,7 +7075,7 @@
         <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G122" t="n">
         <v>30</v>
@@ -7110,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G123" t="n">
         <v>30</v>
@@ -7145,7 +7145,7 @@
         <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G124" t="n">
         <v>30</v>
@@ -7180,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="F125" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G125" t="n">
         <v>30</v>
@@ -7215,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G126" t="n">
         <v>30</v>
@@ -7250,7 +7250,7 @@
         <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.2509769079423544</v>
+        <v>0.2509769079423547</v>
       </c>
       <c r="G127" t="n">
         <v>30</v>
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G170" t="n">
         <v>30</v>
@@ -8790,7 +8790,7 @@
         <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G171" t="n">
         <v>30</v>
@@ -8825,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G172" t="n">
         <v>30</v>
@@ -8860,7 +8860,7 @@
         <v>1</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G173" t="n">
         <v>30</v>
@@ -8895,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G174" t="n">
         <v>30</v>
@@ -8930,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G175" t="n">
         <v>30</v>
@@ -8965,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="F176" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G176" t="n">
         <v>30</v>
@@ -9000,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G177" t="n">
         <v>30</v>
@@ -9035,7 +9035,7 @@
         <v>1</v>
       </c>
       <c r="F178" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G178" t="n">
         <v>30</v>
@@ -9070,7 +9070,7 @@
         <v>1</v>
       </c>
       <c r="F179" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G179" t="n">
         <v>30</v>
@@ -9105,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="F180" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G180" t="n">
         <v>30</v>
@@ -9140,7 +9140,7 @@
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G181" t="n">
         <v>30</v>
@@ -9175,7 +9175,7 @@
         <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G182" t="n">
         <v>30</v>
@@ -9210,7 +9210,7 @@
         <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0.3115364456446941</v>
+        <v>0.3115364456446945</v>
       </c>
       <c r="G183" t="n">
         <v>30</v>
@@ -9245,7 +9245,7 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G184" t="n">
         <v>30</v>
@@ -9280,7 +9280,7 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G185" t="n">
         <v>30</v>
@@ -9315,7 +9315,7 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G186" t="n">
         <v>30</v>
@@ -9350,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G187" t="n">
         <v>30</v>
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G188" t="n">
         <v>30</v>
@@ -9420,7 +9420,7 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G189" t="n">
         <v>30</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G190" t="n">
         <v>30</v>
@@ -9490,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G191" t="n">
         <v>30</v>
@@ -9525,7 +9525,7 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G192" t="n">
         <v>30</v>
@@ -9560,7 +9560,7 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G193" t="n">
         <v>30</v>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G194" t="n">
         <v>30</v>
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G195" t="n">
         <v>30</v>
@@ -9665,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G196" t="n">
         <v>30</v>
@@ -9700,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.6122137226253059</v>
+        <v>0.6122137226253055</v>
       </c>
       <c r="G197" t="n">
         <v>30</v>
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G240" t="n">
         <v>30</v>
@@ -11240,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G241" t="n">
         <v>30</v>
@@ -11275,7 +11275,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G242" t="n">
         <v>30</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G243" t="n">
         <v>30</v>
@@ -11345,7 +11345,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G244" t="n">
         <v>30</v>
@@ -11380,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G245" t="n">
         <v>30</v>
@@ -11415,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G246" t="n">
         <v>30</v>
@@ -11450,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G247" t="n">
         <v>30</v>
@@ -11485,7 +11485,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G248" t="n">
         <v>30</v>
@@ -11520,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G249" t="n">
         <v>30</v>
@@ -11555,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G250" t="n">
         <v>30</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G251" t="n">
         <v>30</v>
@@ -11625,7 +11625,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G252" t="n">
         <v>30</v>
@@ -11660,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>0.5651629154185405</v>
+        <v>0.5651629154185402</v>
       </c>
       <c r="G253" t="n">
         <v>30</v>
@@ -12185,7 +12185,7 @@
         <v>0</v>
       </c>
       <c r="F268" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G268" t="n">
         <v>30</v>
@@ -12220,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G269" t="n">
         <v>30</v>
@@ -12255,7 +12255,7 @@
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G270" t="n">
         <v>30</v>
@@ -12290,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="F271" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G271" t="n">
         <v>30</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G272" t="n">
         <v>30</v>
@@ -12360,7 +12360,7 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G273" t="n">
         <v>30</v>
@@ -12395,7 +12395,7 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G274" t="n">
         <v>30</v>
@@ -12430,7 +12430,7 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G275" t="n">
         <v>30</v>
@@ -12465,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G276" t="n">
         <v>30</v>
@@ -12500,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G277" t="n">
         <v>30</v>
@@ -12535,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G278" t="n">
         <v>30</v>
@@ -12570,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G279" t="n">
         <v>30</v>
@@ -12605,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G280" t="n">
         <v>30</v>
@@ -12640,7 +12640,7 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0.4041894705462791</v>
+        <v>0.4041894705462787</v>
       </c>
       <c r="G281" t="n">
         <v>30</v>
@@ -13655,7 +13655,7 @@
         <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G310" t="n">
         <v>30</v>
@@ -13690,7 +13690,7 @@
         <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G311" t="n">
         <v>30</v>
@@ -13725,7 +13725,7 @@
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G312" t="n">
         <v>30</v>
@@ -13760,7 +13760,7 @@
         <v>1</v>
       </c>
       <c r="F313" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G313" t="n">
         <v>30</v>
@@ -13795,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G314" t="n">
         <v>30</v>
@@ -13830,7 +13830,7 @@
         <v>1</v>
       </c>
       <c r="F315" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G315" t="n">
         <v>30</v>
@@ -13865,7 +13865,7 @@
         <v>1</v>
       </c>
       <c r="F316" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G316" t="n">
         <v>30</v>
@@ -13900,7 +13900,7 @@
         <v>1</v>
       </c>
       <c r="F317" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G317" t="n">
         <v>30</v>
@@ -13935,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="F318" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G318" t="n">
         <v>30</v>
@@ -13970,7 +13970,7 @@
         <v>1</v>
       </c>
       <c r="F319" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G319" t="n">
         <v>30</v>
@@ -14005,7 +14005,7 @@
         <v>1</v>
       </c>
       <c r="F320" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G320" t="n">
         <v>30</v>
@@ -14040,7 +14040,7 @@
         <v>1</v>
       </c>
       <c r="F321" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G321" t="n">
         <v>30</v>
@@ -14075,7 +14075,7 @@
         <v>1</v>
       </c>
       <c r="F322" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G322" t="n">
         <v>30</v>
@@ -14110,7 +14110,7 @@
         <v>1</v>
       </c>
       <c r="F323" t="n">
-        <v>0.4129113045114304</v>
+        <v>0.4129113045114308</v>
       </c>
       <c r="G323" t="n">
         <v>30</v>
@@ -14635,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="F338" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G338" t="n">
         <v>30</v>
@@ -14670,7 +14670,7 @@
         <v>1</v>
       </c>
       <c r="F339" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G339" t="n">
         <v>30</v>
@@ -14705,7 +14705,7 @@
         <v>1</v>
       </c>
       <c r="F340" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G340" t="n">
         <v>30</v>
@@ -14740,7 +14740,7 @@
         <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G341" t="n">
         <v>30</v>
@@ -14775,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="F342" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G342" t="n">
         <v>30</v>
@@ -14810,7 +14810,7 @@
         <v>1</v>
       </c>
       <c r="F343" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G343" t="n">
         <v>30</v>
@@ -14845,7 +14845,7 @@
         <v>1</v>
       </c>
       <c r="F344" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G344" t="n">
         <v>30</v>
@@ -14880,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="F345" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G345" t="n">
         <v>30</v>
@@ -14915,7 +14915,7 @@
         <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G346" t="n">
         <v>30</v>
@@ -14950,7 +14950,7 @@
         <v>1</v>
       </c>
       <c r="F347" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G347" t="n">
         <v>30</v>
@@ -14985,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G348" t="n">
         <v>30</v>
@@ -15020,7 +15020,7 @@
         <v>1</v>
       </c>
       <c r="F349" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G349" t="n">
         <v>30</v>
@@ -15055,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="F350" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G350" t="n">
         <v>30</v>
@@ -15090,7 +15090,7 @@
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>0.4416069698970794</v>
+        <v>0.4416069698970796</v>
       </c>
       <c r="G351" t="n">
         <v>30</v>
@@ -15125,7 +15125,7 @@
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G352" t="n">
         <v>30</v>
@@ -15160,7 +15160,7 @@
         <v>0</v>
       </c>
       <c r="F353" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G353" t="n">
         <v>30</v>
@@ -15195,7 +15195,7 @@
         <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G354" t="n">
         <v>30</v>
@@ -15230,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="F355" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G355" t="n">
         <v>30</v>
@@ -15265,7 +15265,7 @@
         <v>0</v>
       </c>
       <c r="F356" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G356" t="n">
         <v>30</v>
@@ -15300,7 +15300,7 @@
         <v>0</v>
       </c>
       <c r="F357" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G357" t="n">
         <v>30</v>
@@ -15335,7 +15335,7 @@
         <v>0</v>
       </c>
       <c r="F358" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G358" t="n">
         <v>30</v>
@@ -15370,7 +15370,7 @@
         <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G359" t="n">
         <v>30</v>
@@ -15405,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G360" t="n">
         <v>30</v>
@@ -15440,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="F361" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G361" t="n">
         <v>30</v>
@@ -15475,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="F362" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G362" t="n">
         <v>30</v>
@@ -15510,7 +15510,7 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G363" t="n">
         <v>30</v>
@@ -15545,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G364" t="n">
         <v>30</v>
@@ -15580,7 +15580,7 @@
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>0.7298042788410357</v>
+        <v>0.7298042788410356</v>
       </c>
       <c r="G365" t="n">
         <v>30</v>
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
       <c r="F408" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G408" t="n">
         <v>30</v>
@@ -17120,7 +17120,7 @@
         <v>0</v>
       </c>
       <c r="F409" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G409" t="n">
         <v>30</v>
@@ -17155,7 +17155,7 @@
         <v>0</v>
       </c>
       <c r="F410" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G410" t="n">
         <v>30</v>
@@ -17190,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="F411" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G411" t="n">
         <v>30</v>
@@ -17225,7 +17225,7 @@
         <v>0</v>
       </c>
       <c r="F412" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G412" t="n">
         <v>30</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="F413" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G413" t="n">
         <v>30</v>
@@ -17295,7 +17295,7 @@
         <v>0</v>
       </c>
       <c r="F414" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G414" t="n">
         <v>30</v>
@@ -17330,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="F415" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G415" t="n">
         <v>30</v>
@@ -17365,7 +17365,7 @@
         <v>0</v>
       </c>
       <c r="F416" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G416" t="n">
         <v>30</v>
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="F417" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G417" t="n">
         <v>30</v>
@@ -17435,7 +17435,7 @@
         <v>0</v>
       </c>
       <c r="F418" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G418" t="n">
         <v>30</v>
@@ -17470,7 +17470,7 @@
         <v>0</v>
       </c>
       <c r="F419" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G419" t="n">
         <v>30</v>
@@ -17505,7 +17505,7 @@
         <v>0</v>
       </c>
       <c r="F420" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G420" t="n">
         <v>30</v>
@@ -17540,7 +17540,7 @@
         <v>0</v>
       </c>
       <c r="F421" t="n">
-        <v>0.7679006257876382</v>
+        <v>0.7679006257876378</v>
       </c>
       <c r="G421" t="n">
         <v>30</v>
@@ -18065,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="F436" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G436" t="n">
         <v>30</v>
@@ -18100,7 +18100,7 @@
         <v>0</v>
       </c>
       <c r="F437" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G437" t="n">
         <v>30</v>
@@ -18135,7 +18135,7 @@
         <v>0</v>
       </c>
       <c r="F438" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G438" t="n">
         <v>30</v>
@@ -18170,7 +18170,7 @@
         <v>0</v>
       </c>
       <c r="F439" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G439" t="n">
         <v>30</v>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
       <c r="F440" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G440" t="n">
         <v>30</v>
@@ -18240,7 +18240,7 @@
         <v>0</v>
       </c>
       <c r="F441" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G441" t="n">
         <v>30</v>
@@ -18275,7 +18275,7 @@
         <v>0</v>
       </c>
       <c r="F442" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G442" t="n">
         <v>30</v>
@@ -18310,7 +18310,7 @@
         <v>0</v>
       </c>
       <c r="F443" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G443" t="n">
         <v>30</v>
@@ -18345,7 +18345,7 @@
         <v>0</v>
       </c>
       <c r="F444" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G444" t="n">
         <v>30</v>
@@ -18380,7 +18380,7 @@
         <v>0</v>
       </c>
       <c r="F445" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G445" t="n">
         <v>30</v>
@@ -18415,7 +18415,7 @@
         <v>0</v>
       </c>
       <c r="F446" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G446" t="n">
         <v>30</v>
@@ -18450,7 +18450,7 @@
         <v>0</v>
       </c>
       <c r="F447" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G447" t="n">
         <v>30</v>
@@ -18485,7 +18485,7 @@
         <v>0</v>
       </c>
       <c r="F448" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G448" t="n">
         <v>30</v>
@@ -18520,7 +18520,7 @@
         <v>0</v>
       </c>
       <c r="F449" t="n">
-        <v>0.3064468083320389</v>
+        <v>0.3064468083320387</v>
       </c>
       <c r="G449" t="n">
         <v>30</v>
@@ -18555,7 +18555,7 @@
         <v>1</v>
       </c>
       <c r="F450" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G450" t="n">
         <v>30</v>
@@ -18590,7 +18590,7 @@
         <v>1</v>
       </c>
       <c r="F451" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G451" t="n">
         <v>30</v>
@@ -18625,7 +18625,7 @@
         <v>1</v>
       </c>
       <c r="F452" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G452" t="n">
         <v>30</v>
@@ -18660,7 +18660,7 @@
         <v>1</v>
       </c>
       <c r="F453" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G453" t="n">
         <v>30</v>
@@ -18695,7 +18695,7 @@
         <v>1</v>
       </c>
       <c r="F454" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G454" t="n">
         <v>30</v>
@@ -18730,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="F455" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G455" t="n">
         <v>30</v>
@@ -18765,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="F456" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G456" t="n">
         <v>30</v>
@@ -18800,7 +18800,7 @@
         <v>1</v>
       </c>
       <c r="F457" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G457" t="n">
         <v>30</v>
@@ -18835,7 +18835,7 @@
         <v>1</v>
       </c>
       <c r="F458" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G458" t="n">
         <v>30</v>
@@ -18870,7 +18870,7 @@
         <v>1</v>
       </c>
       <c r="F459" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G459" t="n">
         <v>30</v>
@@ -18905,7 +18905,7 @@
         <v>1</v>
       </c>
       <c r="F460" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G460" t="n">
         <v>30</v>
@@ -18940,7 +18940,7 @@
         <v>1</v>
       </c>
       <c r="F461" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G461" t="n">
         <v>30</v>
@@ -18975,7 +18975,7 @@
         <v>1</v>
       </c>
       <c r="F462" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G462" t="n">
         <v>30</v>
@@ -19010,7 +19010,7 @@
         <v>1</v>
       </c>
       <c r="F463" t="n">
-        <v>0.3056417338372005</v>
+        <v>0.3056417338372007</v>
       </c>
       <c r="G463" t="n">
         <v>30</v>
@@ -19045,7 +19045,7 @@
         <v>0</v>
       </c>
       <c r="F464" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G464" t="n">
         <v>30</v>
@@ -19080,7 +19080,7 @@
         <v>0</v>
       </c>
       <c r="F465" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G465" t="n">
         <v>30</v>
@@ -19115,7 +19115,7 @@
         <v>0</v>
       </c>
       <c r="F466" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G466" t="n">
         <v>30</v>
@@ -19150,7 +19150,7 @@
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G467" t="n">
         <v>30</v>
@@ -19185,7 +19185,7 @@
         <v>0</v>
       </c>
       <c r="F468" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G468" t="n">
         <v>30</v>
@@ -19220,7 +19220,7 @@
         <v>0</v>
       </c>
       <c r="F469" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G469" t="n">
         <v>30</v>
@@ -19255,7 +19255,7 @@
         <v>0</v>
       </c>
       <c r="F470" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G470" t="n">
         <v>30</v>
@@ -19290,7 +19290,7 @@
         <v>0</v>
       </c>
       <c r="F471" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G471" t="n">
         <v>30</v>
@@ -19325,7 +19325,7 @@
         <v>0</v>
       </c>
       <c r="F472" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G472" t="n">
         <v>30</v>
@@ -19360,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="F473" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G473" t="n">
         <v>30</v>
@@ -19395,7 +19395,7 @@
         <v>0</v>
       </c>
       <c r="F474" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G474" t="n">
         <v>30</v>
@@ -19430,7 +19430,7 @@
         <v>0</v>
       </c>
       <c r="F475" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G475" t="n">
         <v>30</v>
@@ -19465,7 +19465,7 @@
         <v>0</v>
       </c>
       <c r="F476" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G476" t="n">
         <v>30</v>
@@ -19500,7 +19500,7 @@
         <v>0</v>
       </c>
       <c r="F477" t="n">
-        <v>0.842640035813199</v>
+        <v>0.8426400358131989</v>
       </c>
       <c r="G477" t="n">
         <v>30</v>
@@ -20025,7 +20025,7 @@
         <v>0</v>
       </c>
       <c r="F492" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G492" t="n">
         <v>30</v>
@@ -20060,7 +20060,7 @@
         <v>0</v>
       </c>
       <c r="F493" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G493" t="n">
         <v>30</v>
@@ -20095,7 +20095,7 @@
         <v>0</v>
       </c>
       <c r="F494" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G494" t="n">
         <v>30</v>
@@ -20130,7 +20130,7 @@
         <v>0</v>
       </c>
       <c r="F495" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G495" t="n">
         <v>30</v>
@@ -20165,7 +20165,7 @@
         <v>0</v>
       </c>
       <c r="F496" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G496" t="n">
         <v>30</v>
@@ -20200,7 +20200,7 @@
         <v>0</v>
       </c>
       <c r="F497" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G497" t="n">
         <v>30</v>
@@ -20235,7 +20235,7 @@
         <v>0</v>
       </c>
       <c r="F498" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G498" t="n">
         <v>30</v>
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="F499" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G499" t="n">
         <v>30</v>
@@ -20305,7 +20305,7 @@
         <v>0</v>
       </c>
       <c r="F500" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G500" t="n">
         <v>30</v>
@@ -20340,7 +20340,7 @@
         <v>0</v>
       </c>
       <c r="F501" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G501" t="n">
         <v>30</v>
@@ -20375,7 +20375,7 @@
         <v>0</v>
       </c>
       <c r="F502" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G502" t="n">
         <v>30</v>
@@ -20410,7 +20410,7 @@
         <v>0</v>
       </c>
       <c r="F503" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G503" t="n">
         <v>30</v>
@@ -20445,7 +20445,7 @@
         <v>0</v>
       </c>
       <c r="F504" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G504" t="n">
         <v>30</v>
@@ -20480,7 +20480,7 @@
         <v>0</v>
       </c>
       <c r="F505" t="n">
-        <v>0.6523348502255443</v>
+        <v>0.652334850225544</v>
       </c>
       <c r="G505" t="n">
         <v>30</v>
@@ -20515,7 +20515,7 @@
         <v>1</v>
       </c>
       <c r="F506" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G506" t="n">
         <v>30</v>
@@ -20550,7 +20550,7 @@
         <v>1</v>
       </c>
       <c r="F507" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G507" t="n">
         <v>30</v>
@@ -20585,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="F508" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G508" t="n">
         <v>30</v>
@@ -20620,7 +20620,7 @@
         <v>1</v>
       </c>
       <c r="F509" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G509" t="n">
         <v>30</v>
@@ -20655,7 +20655,7 @@
         <v>1</v>
       </c>
       <c r="F510" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G510" t="n">
         <v>30</v>
@@ -20690,7 +20690,7 @@
         <v>1</v>
       </c>
       <c r="F511" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G511" t="n">
         <v>30</v>
@@ -20725,7 +20725,7 @@
         <v>1</v>
       </c>
       <c r="F512" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G512" t="n">
         <v>30</v>
@@ -20760,7 +20760,7 @@
         <v>1</v>
       </c>
       <c r="F513" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G513" t="n">
         <v>30</v>
@@ -20795,7 +20795,7 @@
         <v>1</v>
       </c>
       <c r="F514" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G514" t="n">
         <v>30</v>
@@ -20830,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="F515" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G515" t="n">
         <v>30</v>
@@ -20865,7 +20865,7 @@
         <v>1</v>
       </c>
       <c r="F516" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G516" t="n">
         <v>30</v>
@@ -20900,7 +20900,7 @@
         <v>1</v>
       </c>
       <c r="F517" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G517" t="n">
         <v>30</v>
@@ -20935,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="F518" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G518" t="n">
         <v>30</v>
@@ -20970,7 +20970,7 @@
         <v>1</v>
       </c>
       <c r="F519" t="n">
-        <v>0.3339691506706321</v>
+        <v>0.3339691506706325</v>
       </c>
       <c r="G519" t="n">
         <v>30</v>
@@ -21495,7 +21495,7 @@
         <v>1</v>
       </c>
       <c r="F534" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G534" t="n">
         <v>30</v>
@@ -21530,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="F535" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G535" t="n">
         <v>30</v>
@@ -21565,7 +21565,7 @@
         <v>1</v>
       </c>
       <c r="F536" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G536" t="n">
         <v>30</v>
@@ -21600,7 +21600,7 @@
         <v>1</v>
       </c>
       <c r="F537" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G537" t="n">
         <v>30</v>
@@ -21635,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="F538" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G538" t="n">
         <v>30</v>
@@ -21670,7 +21670,7 @@
         <v>1</v>
       </c>
       <c r="F539" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G539" t="n">
         <v>30</v>
@@ -21705,7 +21705,7 @@
         <v>1</v>
       </c>
       <c r="F540" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G540" t="n">
         <v>30</v>
@@ -21740,7 +21740,7 @@
         <v>1</v>
       </c>
       <c r="F541" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G541" t="n">
         <v>30</v>
@@ -21775,7 +21775,7 @@
         <v>1</v>
       </c>
       <c r="F542" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G542" t="n">
         <v>30</v>
@@ -21810,7 +21810,7 @@
         <v>1</v>
       </c>
       <c r="F543" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G543" t="n">
         <v>30</v>
@@ -21845,7 +21845,7 @@
         <v>1</v>
       </c>
       <c r="F544" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G544" t="n">
         <v>30</v>
@@ -21880,7 +21880,7 @@
         <v>1</v>
       </c>
       <c r="F545" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G545" t="n">
         <v>30</v>
@@ -21915,7 +21915,7 @@
         <v>1</v>
       </c>
       <c r="F546" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G546" t="n">
         <v>30</v>
@@ -21950,7 +21950,7 @@
         <v>1</v>
       </c>
       <c r="F547" t="n">
-        <v>0.3099813021469564</v>
+        <v>0.3099813021469567</v>
       </c>
       <c r="G547" t="n">
         <v>30</v>
@@ -21985,7 +21985,7 @@
         <v>0</v>
       </c>
       <c r="F548" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G548" t="n">
         <v>30</v>
@@ -22020,7 +22020,7 @@
         <v>0</v>
       </c>
       <c r="F549" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G549" t="n">
         <v>30</v>
@@ -22055,7 +22055,7 @@
         <v>0</v>
       </c>
       <c r="F550" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G550" t="n">
         <v>30</v>
@@ -22090,7 +22090,7 @@
         <v>0</v>
       </c>
       <c r="F551" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G551" t="n">
         <v>30</v>
@@ -22125,7 +22125,7 @@
         <v>0</v>
       </c>
       <c r="F552" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G552" t="n">
         <v>30</v>
@@ -22160,7 +22160,7 @@
         <v>0</v>
       </c>
       <c r="F553" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G553" t="n">
         <v>30</v>
@@ -22195,7 +22195,7 @@
         <v>0</v>
       </c>
       <c r="F554" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G554" t="n">
         <v>30</v>
@@ -22230,7 +22230,7 @@
         <v>0</v>
       </c>
       <c r="F555" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G555" t="n">
         <v>30</v>
@@ -22265,7 +22265,7 @@
         <v>0</v>
       </c>
       <c r="F556" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G556" t="n">
         <v>30</v>
@@ -22300,7 +22300,7 @@
         <v>0</v>
       </c>
       <c r="F557" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G557" t="n">
         <v>30</v>
@@ -22335,7 +22335,7 @@
         <v>0</v>
       </c>
       <c r="F558" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G558" t="n">
         <v>30</v>
@@ -22370,7 +22370,7 @@
         <v>0</v>
       </c>
       <c r="F559" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G559" t="n">
         <v>30</v>
@@ -22405,7 +22405,7 @@
         <v>0</v>
       </c>
       <c r="F560" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G560" t="n">
         <v>30</v>
@@ -22440,7 +22440,7 @@
         <v>0</v>
       </c>
       <c r="F561" t="n">
-        <v>0.6206798215778699</v>
+        <v>0.6206798215778697</v>
       </c>
       <c r="G561" t="n">
         <v>30</v>
@@ -23945,7 +23945,7 @@
         <v>0</v>
       </c>
       <c r="F604" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G604" t="n">
         <v>30</v>
@@ -23980,7 +23980,7 @@
         <v>0</v>
       </c>
       <c r="F605" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G605" t="n">
         <v>30</v>
@@ -24015,7 +24015,7 @@
         <v>0</v>
       </c>
       <c r="F606" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G606" t="n">
         <v>30</v>
@@ -24050,7 +24050,7 @@
         <v>0</v>
       </c>
       <c r="F607" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G607" t="n">
         <v>30</v>
@@ -24085,7 +24085,7 @@
         <v>0</v>
       </c>
       <c r="F608" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G608" t="n">
         <v>30</v>
@@ -24120,7 +24120,7 @@
         <v>0</v>
       </c>
       <c r="F609" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G609" t="n">
         <v>30</v>
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="F610" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G610" t="n">
         <v>30</v>
@@ -24190,7 +24190,7 @@
         <v>0</v>
       </c>
       <c r="F611" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G611" t="n">
         <v>30</v>
@@ -24225,7 +24225,7 @@
         <v>0</v>
       </c>
       <c r="F612" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G612" t="n">
         <v>30</v>
@@ -24260,7 +24260,7 @@
         <v>0</v>
       </c>
       <c r="F613" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G613" t="n">
         <v>30</v>
@@ -24295,7 +24295,7 @@
         <v>0</v>
       </c>
       <c r="F614" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G614" t="n">
         <v>30</v>
@@ -24330,7 +24330,7 @@
         <v>0</v>
       </c>
       <c r="F615" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G615" t="n">
         <v>30</v>
@@ -24365,7 +24365,7 @@
         <v>0</v>
       </c>
       <c r="F616" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G616" t="n">
         <v>30</v>
@@ -24400,7 +24400,7 @@
         <v>0</v>
       </c>
       <c r="F617" t="n">
-        <v>0.3133322401872006</v>
+        <v>0.3133322401872002</v>
       </c>
       <c r="G617" t="n">
         <v>30</v>
@@ -26885,7 +26885,7 @@
         <v>0</v>
       </c>
       <c r="F688" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G688" t="n">
         <v>30</v>
@@ -26920,7 +26920,7 @@
         <v>0</v>
       </c>
       <c r="F689" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G689" t="n">
         <v>30</v>
@@ -26955,7 +26955,7 @@
         <v>0</v>
       </c>
       <c r="F690" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G690" t="n">
         <v>30</v>
@@ -26990,7 +26990,7 @@
         <v>0</v>
       </c>
       <c r="F691" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G691" t="n">
         <v>30</v>
@@ -27025,7 +27025,7 @@
         <v>0</v>
       </c>
       <c r="F692" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G692" t="n">
         <v>30</v>
@@ -27060,7 +27060,7 @@
         <v>0</v>
       </c>
       <c r="F693" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G693" t="n">
         <v>30</v>
@@ -27095,7 +27095,7 @@
         <v>0</v>
       </c>
       <c r="F694" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G694" t="n">
         <v>30</v>
@@ -27130,7 +27130,7 @@
         <v>0</v>
       </c>
       <c r="F695" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G695" t="n">
         <v>30</v>
@@ -27165,7 +27165,7 @@
         <v>0</v>
       </c>
       <c r="F696" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G696" t="n">
         <v>30</v>
@@ -27200,7 +27200,7 @@
         <v>0</v>
       </c>
       <c r="F697" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G697" t="n">
         <v>30</v>
@@ -27235,7 +27235,7 @@
         <v>0</v>
       </c>
       <c r="F698" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G698" t="n">
         <v>30</v>
@@ -27270,7 +27270,7 @@
         <v>0</v>
       </c>
       <c r="F699" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G699" t="n">
         <v>30</v>
@@ -27305,7 +27305,7 @@
         <v>0</v>
       </c>
       <c r="F700" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G700" t="n">
         <v>30</v>
@@ -27340,7 +27340,7 @@
         <v>0</v>
       </c>
       <c r="F701" t="n">
-        <v>0.7042600452005728</v>
+        <v>0.7042600452005726</v>
       </c>
       <c r="G701" t="n">
         <v>30</v>
@@ -27375,7 +27375,7 @@
         <v>1</v>
       </c>
       <c r="F702" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G702" t="n">
         <v>30</v>
@@ -27410,7 +27410,7 @@
         <v>1</v>
       </c>
       <c r="F703" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G703" t="n">
         <v>30</v>
@@ -27445,7 +27445,7 @@
         <v>1</v>
       </c>
       <c r="F704" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G704" t="n">
         <v>30</v>
@@ -27480,7 +27480,7 @@
         <v>1</v>
       </c>
       <c r="F705" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G705" t="n">
         <v>30</v>
@@ -27515,7 +27515,7 @@
         <v>1</v>
       </c>
       <c r="F706" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G706" t="n">
         <v>30</v>
@@ -27550,7 +27550,7 @@
         <v>1</v>
       </c>
       <c r="F707" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G707" t="n">
         <v>30</v>
@@ -27585,7 +27585,7 @@
         <v>1</v>
       </c>
       <c r="F708" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G708" t="n">
         <v>30</v>
@@ -27620,7 +27620,7 @@
         <v>1</v>
       </c>
       <c r="F709" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G709" t="n">
         <v>30</v>
@@ -27655,7 +27655,7 @@
         <v>1</v>
       </c>
       <c r="F710" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G710" t="n">
         <v>30</v>
@@ -27690,7 +27690,7 @@
         <v>1</v>
       </c>
       <c r="F711" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G711" t="n">
         <v>30</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="F712" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G712" t="n">
         <v>30</v>
@@ -27760,7 +27760,7 @@
         <v>1</v>
       </c>
       <c r="F713" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G713" t="n">
         <v>30</v>
@@ -27795,7 +27795,7 @@
         <v>1</v>
       </c>
       <c r="F714" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G714" t="n">
         <v>30</v>
@@ -27830,7 +27830,7 @@
         <v>1</v>
       </c>
       <c r="F715" t="n">
-        <v>0.426314527038833</v>
+        <v>0.4263145270388333</v>
       </c>
       <c r="G715" t="n">
         <v>30</v>
@@ -28355,7 +28355,7 @@
         <v>1</v>
       </c>
       <c r="F730" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G730" t="n">
         <v>30</v>
@@ -28390,7 +28390,7 @@
         <v>1</v>
       </c>
       <c r="F731" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G731" t="n">
         <v>30</v>
@@ -28425,7 +28425,7 @@
         <v>1</v>
       </c>
       <c r="F732" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G732" t="n">
         <v>30</v>
@@ -28460,7 +28460,7 @@
         <v>1</v>
       </c>
       <c r="F733" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G733" t="n">
         <v>30</v>
@@ -28495,7 +28495,7 @@
         <v>1</v>
       </c>
       <c r="F734" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G734" t="n">
         <v>30</v>
@@ -28530,7 +28530,7 @@
         <v>1</v>
       </c>
       <c r="F735" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G735" t="n">
         <v>30</v>
@@ -28565,7 +28565,7 @@
         <v>1</v>
       </c>
       <c r="F736" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G736" t="n">
         <v>30</v>
@@ -28600,7 +28600,7 @@
         <v>1</v>
       </c>
       <c r="F737" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G737" t="n">
         <v>30</v>
@@ -28635,7 +28635,7 @@
         <v>1</v>
       </c>
       <c r="F738" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G738" t="n">
         <v>30</v>
@@ -28670,7 +28670,7 @@
         <v>1</v>
       </c>
       <c r="F739" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G739" t="n">
         <v>30</v>
@@ -28705,7 +28705,7 @@
         <v>1</v>
       </c>
       <c r="F740" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G740" t="n">
         <v>30</v>
@@ -28740,7 +28740,7 @@
         <v>1</v>
       </c>
       <c r="F741" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G741" t="n">
         <v>30</v>
@@ -28775,7 +28775,7 @@
         <v>1</v>
       </c>
       <c r="F742" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G742" t="n">
         <v>30</v>
@@ -28810,7 +28810,7 @@
         <v>1</v>
       </c>
       <c r="F743" t="n">
-        <v>0.2653167987405222</v>
+        <v>0.2653167987405221</v>
       </c>
       <c r="G743" t="n">
         <v>30</v>
@@ -28845,7 +28845,7 @@
         <v>0</v>
       </c>
       <c r="F744" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G744" t="n">
         <v>30</v>
@@ -28880,7 +28880,7 @@
         <v>0</v>
       </c>
       <c r="F745" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G745" t="n">
         <v>30</v>
@@ -28915,7 +28915,7 @@
         <v>0</v>
       </c>
       <c r="F746" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G746" t="n">
         <v>30</v>
@@ -28950,7 +28950,7 @@
         <v>0</v>
       </c>
       <c r="F747" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G747" t="n">
         <v>30</v>
@@ -28985,7 +28985,7 @@
         <v>0</v>
       </c>
       <c r="F748" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G748" t="n">
         <v>30</v>
@@ -29020,7 +29020,7 @@
         <v>0</v>
       </c>
       <c r="F749" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G749" t="n">
         <v>30</v>
@@ -29055,7 +29055,7 @@
         <v>0</v>
       </c>
       <c r="F750" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G750" t="n">
         <v>30</v>
@@ -29090,7 +29090,7 @@
         <v>0</v>
       </c>
       <c r="F751" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G751" t="n">
         <v>30</v>
@@ -29125,7 +29125,7 @@
         <v>0</v>
       </c>
       <c r="F752" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G752" t="n">
         <v>30</v>
@@ -29160,7 +29160,7 @@
         <v>0</v>
       </c>
       <c r="F753" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G753" t="n">
         <v>30</v>
@@ -29195,7 +29195,7 @@
         <v>0</v>
       </c>
       <c r="F754" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G754" t="n">
         <v>30</v>
@@ -29230,7 +29230,7 @@
         <v>0</v>
       </c>
       <c r="F755" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G755" t="n">
         <v>30</v>
@@ -29265,7 +29265,7 @@
         <v>0</v>
       </c>
       <c r="F756" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G756" t="n">
         <v>30</v>
@@ -29300,7 +29300,7 @@
         <v>0</v>
       </c>
       <c r="F757" t="n">
-        <v>0.6281397714709058</v>
+        <v>0.6281397714709057</v>
       </c>
       <c r="G757" t="n">
         <v>30</v>
@@ -29825,7 +29825,7 @@
         <v>0</v>
       </c>
       <c r="F772" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G772" t="n">
         <v>30</v>
@@ -29860,7 +29860,7 @@
         <v>0</v>
       </c>
       <c r="F773" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G773" t="n">
         <v>30</v>
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="F774" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G774" t="n">
         <v>30</v>
@@ -29930,7 +29930,7 @@
         <v>0</v>
       </c>
       <c r="F775" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G775" t="n">
         <v>30</v>
@@ -29965,7 +29965,7 @@
         <v>0</v>
       </c>
       <c r="F776" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G776" t="n">
         <v>30</v>
@@ -30000,7 +30000,7 @@
         <v>0</v>
       </c>
       <c r="F777" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G777" t="n">
         <v>30</v>
@@ -30035,7 +30035,7 @@
         <v>0</v>
       </c>
       <c r="F778" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G778" t="n">
         <v>30</v>
@@ -30070,7 +30070,7 @@
         <v>0</v>
       </c>
       <c r="F779" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G779" t="n">
         <v>30</v>
@@ -30105,7 +30105,7 @@
         <v>0</v>
       </c>
       <c r="F780" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G780" t="n">
         <v>30</v>
@@ -30140,7 +30140,7 @@
         <v>0</v>
       </c>
       <c r="F781" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G781" t="n">
         <v>30</v>
@@ -30175,7 +30175,7 @@
         <v>0</v>
       </c>
       <c r="F782" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G782" t="n">
         <v>30</v>
@@ -30210,7 +30210,7 @@
         <v>0</v>
       </c>
       <c r="F783" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G783" t="n">
         <v>30</v>
@@ -30245,7 +30245,7 @@
         <v>0</v>
       </c>
       <c r="F784" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G784" t="n">
         <v>30</v>
@@ -30280,7 +30280,7 @@
         <v>0</v>
       </c>
       <c r="F785" t="n">
-        <v>0.3705643334055078</v>
+        <v>0.3705643334055075</v>
       </c>
       <c r="G785" t="n">
         <v>30</v>
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="F800" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G800" t="n">
         <v>30</v>
@@ -30840,7 +30840,7 @@
         <v>0</v>
       </c>
       <c r="F801" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G801" t="n">
         <v>30</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="F802" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G802" t="n">
         <v>30</v>
@@ -30910,7 +30910,7 @@
         <v>0</v>
       </c>
       <c r="F803" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G803" t="n">
         <v>30</v>
@@ -30945,7 +30945,7 @@
         <v>0</v>
       </c>
       <c r="F804" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G804" t="n">
         <v>30</v>
@@ -30980,7 +30980,7 @@
         <v>0</v>
       </c>
       <c r="F805" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G805" t="n">
         <v>30</v>
@@ -31015,7 +31015,7 @@
         <v>0</v>
       </c>
       <c r="F806" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G806" t="n">
         <v>30</v>
@@ -31050,7 +31050,7 @@
         <v>0</v>
       </c>
       <c r="F807" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G807" t="n">
         <v>30</v>
@@ -31085,7 +31085,7 @@
         <v>0</v>
       </c>
       <c r="F808" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G808" t="n">
         <v>30</v>
@@ -31120,7 +31120,7 @@
         <v>0</v>
       </c>
       <c r="F809" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G809" t="n">
         <v>30</v>
@@ -31155,7 +31155,7 @@
         <v>0</v>
       </c>
       <c r="F810" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G810" t="n">
         <v>30</v>
@@ -31190,7 +31190,7 @@
         <v>0</v>
       </c>
       <c r="F811" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G811" t="n">
         <v>30</v>
@@ -31225,7 +31225,7 @@
         <v>0</v>
       </c>
       <c r="F812" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G812" t="n">
         <v>30</v>
@@ -31260,7 +31260,7 @@
         <v>0</v>
       </c>
       <c r="F813" t="n">
-        <v>0.4395080729069757</v>
+        <v>0.4395080729069752</v>
       </c>
       <c r="G813" t="n">
         <v>30</v>
@@ -31295,7 +31295,7 @@
         <v>1</v>
       </c>
       <c r="F814" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G814" t="n">
         <v>30</v>
@@ -31330,7 +31330,7 @@
         <v>1</v>
       </c>
       <c r="F815" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G815" t="n">
         <v>30</v>
@@ -31365,7 +31365,7 @@
         <v>1</v>
       </c>
       <c r="F816" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G816" t="n">
         <v>30</v>
@@ -31400,7 +31400,7 @@
         <v>1</v>
       </c>
       <c r="F817" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G817" t="n">
         <v>30</v>
@@ -31435,7 +31435,7 @@
         <v>1</v>
       </c>
       <c r="F818" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G818" t="n">
         <v>30</v>
@@ -31470,7 +31470,7 @@
         <v>1</v>
       </c>
       <c r="F819" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G819" t="n">
         <v>30</v>
@@ -31505,7 +31505,7 @@
         <v>1</v>
       </c>
       <c r="F820" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G820" t="n">
         <v>30</v>
@@ -31540,7 +31540,7 @@
         <v>1</v>
       </c>
       <c r="F821" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G821" t="n">
         <v>30</v>
@@ -31575,7 +31575,7 @@
         <v>1</v>
       </c>
       <c r="F822" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G822" t="n">
         <v>30</v>
@@ -31610,7 +31610,7 @@
         <v>1</v>
       </c>
       <c r="F823" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G823" t="n">
         <v>30</v>
@@ -31645,7 +31645,7 @@
         <v>1</v>
       </c>
       <c r="F824" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G824" t="n">
         <v>30</v>
@@ -31680,7 +31680,7 @@
         <v>1</v>
       </c>
       <c r="F825" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G825" t="n">
         <v>30</v>
@@ -31715,7 +31715,7 @@
         <v>1</v>
       </c>
       <c r="F826" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G826" t="n">
         <v>30</v>
@@ -31750,7 +31750,7 @@
         <v>1</v>
       </c>
       <c r="F827" t="n">
-        <v>0.3305532602160361</v>
+        <v>0.3305532602160365</v>
       </c>
       <c r="G827" t="n">
         <v>30</v>
@@ -32275,7 +32275,7 @@
         <v>1</v>
       </c>
       <c r="F842" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G842" t="n">
         <v>30</v>
@@ -32310,7 +32310,7 @@
         <v>1</v>
       </c>
       <c r="F843" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G843" t="n">
         <v>30</v>
@@ -32345,7 +32345,7 @@
         <v>1</v>
       </c>
       <c r="F844" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G844" t="n">
         <v>30</v>
@@ -32380,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="F845" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G845" t="n">
         <v>30</v>
@@ -32415,7 +32415,7 @@
         <v>1</v>
       </c>
       <c r="F846" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G846" t="n">
         <v>30</v>
@@ -32450,7 +32450,7 @@
         <v>1</v>
       </c>
       <c r="F847" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G847" t="n">
         <v>30</v>
@@ -32485,7 +32485,7 @@
         <v>1</v>
       </c>
       <c r="F848" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G848" t="n">
         <v>30</v>
@@ -32520,7 +32520,7 @@
         <v>1</v>
       </c>
       <c r="F849" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G849" t="n">
         <v>30</v>
@@ -32555,7 +32555,7 @@
         <v>1</v>
       </c>
       <c r="F850" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G850" t="n">
         <v>30</v>
@@ -32590,7 +32590,7 @@
         <v>1</v>
       </c>
       <c r="F851" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G851" t="n">
         <v>30</v>
@@ -32625,7 +32625,7 @@
         <v>1</v>
       </c>
       <c r="F852" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G852" t="n">
         <v>30</v>
@@ -32660,7 +32660,7 @@
         <v>1</v>
       </c>
       <c r="F853" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G853" t="n">
         <v>30</v>
@@ -32695,7 +32695,7 @@
         <v>1</v>
       </c>
       <c r="F854" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G854" t="n">
         <v>30</v>
@@ -32730,7 +32730,7 @@
         <v>1</v>
       </c>
       <c r="F855" t="n">
-        <v>0.3267792574532766</v>
+        <v>0.326779257453277</v>
       </c>
       <c r="G855" t="n">
         <v>30</v>
@@ -33255,7 +33255,7 @@
         <v>1</v>
       </c>
       <c r="F870" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G870" t="n">
         <v>30</v>
@@ -33290,7 +33290,7 @@
         <v>1</v>
       </c>
       <c r="F871" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G871" t="n">
         <v>30</v>
@@ -33325,7 +33325,7 @@
         <v>1</v>
       </c>
       <c r="F872" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G872" t="n">
         <v>30</v>
@@ -33360,7 +33360,7 @@
         <v>1</v>
       </c>
       <c r="F873" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G873" t="n">
         <v>30</v>
@@ -33395,7 +33395,7 @@
         <v>1</v>
       </c>
       <c r="F874" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G874" t="n">
         <v>30</v>
@@ -33430,7 +33430,7 @@
         <v>1</v>
       </c>
       <c r="F875" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G875" t="n">
         <v>30</v>
@@ -33465,7 +33465,7 @@
         <v>1</v>
       </c>
       <c r="F876" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G876" t="n">
         <v>30</v>
@@ -33500,7 +33500,7 @@
         <v>1</v>
       </c>
       <c r="F877" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G877" t="n">
         <v>30</v>
@@ -33535,7 +33535,7 @@
         <v>1</v>
       </c>
       <c r="F878" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G878" t="n">
         <v>30</v>
@@ -33570,7 +33570,7 @@
         <v>1</v>
       </c>
       <c r="F879" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G879" t="n">
         <v>30</v>
@@ -33605,7 +33605,7 @@
         <v>1</v>
       </c>
       <c r="F880" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G880" t="n">
         <v>30</v>
@@ -33640,7 +33640,7 @@
         <v>1</v>
       </c>
       <c r="F881" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G881" t="n">
         <v>30</v>
@@ -33675,7 +33675,7 @@
         <v>1</v>
       </c>
       <c r="F882" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G882" t="n">
         <v>30</v>
@@ -33710,7 +33710,7 @@
         <v>1</v>
       </c>
       <c r="F883" t="n">
-        <v>0.3166167335403818</v>
+        <v>0.3166167335403822</v>
       </c>
       <c r="G883" t="n">
         <v>30</v>
@@ -34725,7 +34725,7 @@
         <v>0</v>
       </c>
       <c r="F912" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G912" t="n">
         <v>30</v>
@@ -34760,7 +34760,7 @@
         <v>0</v>
       </c>
       <c r="F913" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G913" t="n">
         <v>30</v>
@@ -34795,7 +34795,7 @@
         <v>0</v>
       </c>
       <c r="F914" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G914" t="n">
         <v>30</v>
@@ -34830,7 +34830,7 @@
         <v>0</v>
       </c>
       <c r="F915" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G915" t="n">
         <v>30</v>
@@ -34865,7 +34865,7 @@
         <v>0</v>
       </c>
       <c r="F916" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G916" t="n">
         <v>30</v>
@@ -34900,7 +34900,7 @@
         <v>0</v>
       </c>
       <c r="F917" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G917" t="n">
         <v>30</v>
@@ -34935,7 +34935,7 @@
         <v>0</v>
       </c>
       <c r="F918" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G918" t="n">
         <v>30</v>
@@ -34970,7 +34970,7 @@
         <v>0</v>
       </c>
       <c r="F919" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G919" t="n">
         <v>30</v>
@@ -35005,7 +35005,7 @@
         <v>0</v>
       </c>
       <c r="F920" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G920" t="n">
         <v>30</v>
@@ -35040,7 +35040,7 @@
         <v>0</v>
       </c>
       <c r="F921" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G921" t="n">
         <v>30</v>
@@ -35075,7 +35075,7 @@
         <v>0</v>
       </c>
       <c r="F922" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G922" t="n">
         <v>30</v>
@@ -35110,7 +35110,7 @@
         <v>0</v>
       </c>
       <c r="F923" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G923" t="n">
         <v>30</v>
@@ -35145,7 +35145,7 @@
         <v>0</v>
       </c>
       <c r="F924" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G924" t="n">
         <v>30</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="F925" t="n">
-        <v>0.5585539401849071</v>
+        <v>0.5585539401849069</v>
       </c>
       <c r="G925" t="n">
         <v>30</v>
@@ -36195,7 +36195,7 @@
         <v>1</v>
       </c>
       <c r="F954" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G954" t="n">
         <v>30</v>
@@ -36230,7 +36230,7 @@
         <v>1</v>
       </c>
       <c r="F955" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G955" t="n">
         <v>30</v>
@@ -36265,7 +36265,7 @@
         <v>1</v>
       </c>
       <c r="F956" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G956" t="n">
         <v>30</v>
@@ -36300,7 +36300,7 @@
         <v>1</v>
       </c>
       <c r="F957" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G957" t="n">
         <v>30</v>
@@ -36335,7 +36335,7 @@
         <v>1</v>
       </c>
       <c r="F958" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G958" t="n">
         <v>30</v>
@@ -36370,7 +36370,7 @@
         <v>1</v>
       </c>
       <c r="F959" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G959" t="n">
         <v>30</v>
@@ -36405,7 +36405,7 @@
         <v>1</v>
       </c>
       <c r="F960" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G960" t="n">
         <v>30</v>
@@ -36440,7 +36440,7 @@
         <v>1</v>
       </c>
       <c r="F961" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G961" t="n">
         <v>30</v>
@@ -36475,7 +36475,7 @@
         <v>1</v>
       </c>
       <c r="F962" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G962" t="n">
         <v>30</v>
@@ -36510,7 +36510,7 @@
         <v>1</v>
       </c>
       <c r="F963" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G963" t="n">
         <v>30</v>
@@ -36545,7 +36545,7 @@
         <v>1</v>
       </c>
       <c r="F964" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G964" t="n">
         <v>30</v>
@@ -36580,7 +36580,7 @@
         <v>1</v>
       </c>
       <c r="F965" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G965" t="n">
         <v>30</v>
@@ -36615,7 +36615,7 @@
         <v>1</v>
       </c>
       <c r="F966" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G966" t="n">
         <v>30</v>
@@ -36650,7 +36650,7 @@
         <v>1</v>
       </c>
       <c r="F967" t="n">
-        <v>0.5984324623317749</v>
+        <v>0.5984324623317754</v>
       </c>
       <c r="G967" t="n">
         <v>30</v>
@@ -36685,7 +36685,7 @@
         <v>0</v>
       </c>
       <c r="F968" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G968" t="n">
         <v>30</v>
@@ -36720,7 +36720,7 @@
         <v>0</v>
       </c>
       <c r="F969" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G969" t="n">
         <v>30</v>
@@ -36755,7 +36755,7 @@
         <v>0</v>
       </c>
       <c r="F970" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G970" t="n">
         <v>30</v>
@@ -36790,7 +36790,7 @@
         <v>0</v>
       </c>
       <c r="F971" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G971" t="n">
         <v>30</v>
@@ -36825,7 +36825,7 @@
         <v>0</v>
       </c>
       <c r="F972" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G972" t="n">
         <v>30</v>
@@ -36860,7 +36860,7 @@
         <v>0</v>
       </c>
       <c r="F973" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G973" t="n">
         <v>30</v>
@@ -36895,7 +36895,7 @@
         <v>0</v>
       </c>
       <c r="F974" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G974" t="n">
         <v>30</v>
@@ -36930,7 +36930,7 @@
         <v>0</v>
       </c>
       <c r="F975" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G975" t="n">
         <v>30</v>
@@ -36965,7 +36965,7 @@
         <v>0</v>
       </c>
       <c r="F976" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G976" t="n">
         <v>30</v>
@@ -37000,7 +37000,7 @@
         <v>0</v>
       </c>
       <c r="F977" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G977" t="n">
         <v>30</v>
@@ -37035,7 +37035,7 @@
         <v>0</v>
       </c>
       <c r="F978" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G978" t="n">
         <v>30</v>
@@ -37070,7 +37070,7 @@
         <v>0</v>
       </c>
       <c r="F979" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G979" t="n">
         <v>30</v>
@@ -37105,7 +37105,7 @@
         <v>0</v>
       </c>
       <c r="F980" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G980" t="n">
         <v>30</v>
@@ -37140,7 +37140,7 @@
         <v>0</v>
       </c>
       <c r="F981" t="n">
-        <v>0.4133172975614326</v>
+        <v>0.4133172975614324</v>
       </c>
       <c r="G981" t="n">
         <v>30</v>
@@ -37665,7 +37665,7 @@
         <v>3</v>
       </c>
       <c r="F996" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G996" t="n">
         <v>30</v>
@@ -37700,7 +37700,7 @@
         <v>3</v>
       </c>
       <c r="F997" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G997" t="n">
         <v>30</v>
@@ -37735,7 +37735,7 @@
         <v>3</v>
       </c>
       <c r="F998" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G998" t="n">
         <v>30</v>
@@ -37770,7 +37770,7 @@
         <v>3</v>
       </c>
       <c r="F999" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G999" t="n">
         <v>30</v>
@@ -37805,7 +37805,7 @@
         <v>3</v>
       </c>
       <c r="F1000" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1000" t="n">
         <v>30</v>
@@ -37840,7 +37840,7 @@
         <v>3</v>
       </c>
       <c r="F1001" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1001" t="n">
         <v>30</v>
@@ -37875,7 +37875,7 @@
         <v>3</v>
       </c>
       <c r="F1002" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1002" t="n">
         <v>30</v>
@@ -37910,7 +37910,7 @@
         <v>3</v>
       </c>
       <c r="F1003" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1003" t="n">
         <v>30</v>
@@ -37945,7 +37945,7 @@
         <v>3</v>
       </c>
       <c r="F1004" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1004" t="n">
         <v>30</v>
@@ -37980,7 +37980,7 @@
         <v>3</v>
       </c>
       <c r="F1005" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1005" t="n">
         <v>30</v>
@@ -38015,7 +38015,7 @@
         <v>3</v>
       </c>
       <c r="F1006" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1006" t="n">
         <v>30</v>
@@ -38050,7 +38050,7 @@
         <v>3</v>
       </c>
       <c r="F1007" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1007" t="n">
         <v>30</v>
@@ -38085,7 +38085,7 @@
         <v>3</v>
       </c>
       <c r="F1008" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1008" t="n">
         <v>30</v>
@@ -38120,7 +38120,7 @@
         <v>3</v>
       </c>
       <c r="F1009" t="n">
-        <v>0.6053764161053445</v>
+        <v>0.6053764161053448</v>
       </c>
       <c r="G1009" t="n">
         <v>30</v>
@@ -38155,7 +38155,7 @@
         <v>1</v>
       </c>
       <c r="F1010" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1010" t="n">
         <v>30</v>
@@ -38190,7 +38190,7 @@
         <v>1</v>
       </c>
       <c r="F1011" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1011" t="n">
         <v>30</v>
@@ -38225,7 +38225,7 @@
         <v>1</v>
       </c>
       <c r="F1012" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1012" t="n">
         <v>30</v>
@@ -38260,7 +38260,7 @@
         <v>1</v>
       </c>
       <c r="F1013" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1013" t="n">
         <v>30</v>
@@ -38295,7 +38295,7 @@
         <v>1</v>
       </c>
       <c r="F1014" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1014" t="n">
         <v>30</v>
@@ -38330,7 +38330,7 @@
         <v>1</v>
       </c>
       <c r="F1015" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1015" t="n">
         <v>30</v>
@@ -38365,7 +38365,7 @@
         <v>1</v>
       </c>
       <c r="F1016" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1016" t="n">
         <v>30</v>
@@ -38400,7 +38400,7 @@
         <v>1</v>
       </c>
       <c r="F1017" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1017" t="n">
         <v>30</v>
@@ -38435,7 +38435,7 @@
         <v>1</v>
       </c>
       <c r="F1018" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1018" t="n">
         <v>30</v>
@@ -38470,7 +38470,7 @@
         <v>1</v>
       </c>
       <c r="F1019" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1019" t="n">
         <v>30</v>
@@ -38505,7 +38505,7 @@
         <v>1</v>
       </c>
       <c r="F1020" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1020" t="n">
         <v>30</v>
@@ -38540,7 +38540,7 @@
         <v>1</v>
       </c>
       <c r="F1021" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1021" t="n">
         <v>30</v>
@@ -38575,7 +38575,7 @@
         <v>1</v>
       </c>
       <c r="F1022" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1022" t="n">
         <v>30</v>
@@ -38610,7 +38610,7 @@
         <v>1</v>
       </c>
       <c r="F1023" t="n">
-        <v>0.423676342275553</v>
+        <v>0.4236763422755528</v>
       </c>
       <c r="G1023" t="n">
         <v>30</v>
@@ -40605,7 +40605,7 @@
         <v>3</v>
       </c>
       <c r="F1080" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1080" t="n">
         <v>30</v>
@@ -40640,7 +40640,7 @@
         <v>3</v>
       </c>
       <c r="F1081" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1081" t="n">
         <v>30</v>
@@ -40675,7 +40675,7 @@
         <v>3</v>
       </c>
       <c r="F1082" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1082" t="n">
         <v>30</v>
@@ -40710,7 +40710,7 @@
         <v>3</v>
       </c>
       <c r="F1083" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1083" t="n">
         <v>30</v>
@@ -40745,7 +40745,7 @@
         <v>3</v>
       </c>
       <c r="F1084" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1084" t="n">
         <v>30</v>
@@ -40780,7 +40780,7 @@
         <v>3</v>
       </c>
       <c r="F1085" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1085" t="n">
         <v>30</v>
@@ -40815,7 +40815,7 @@
         <v>3</v>
       </c>
       <c r="F1086" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1086" t="n">
         <v>30</v>
@@ -40850,7 +40850,7 @@
         <v>3</v>
       </c>
       <c r="F1087" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1087" t="n">
         <v>30</v>
@@ -40885,7 +40885,7 @@
         <v>3</v>
       </c>
       <c r="F1088" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1088" t="n">
         <v>30</v>
@@ -40920,7 +40920,7 @@
         <v>3</v>
       </c>
       <c r="F1089" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1089" t="n">
         <v>30</v>
@@ -40955,7 +40955,7 @@
         <v>3</v>
       </c>
       <c r="F1090" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1090" t="n">
         <v>30</v>
@@ -40990,7 +40990,7 @@
         <v>3</v>
       </c>
       <c r="F1091" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1091" t="n">
         <v>30</v>
@@ -41025,7 +41025,7 @@
         <v>3</v>
       </c>
       <c r="F1092" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1092" t="n">
         <v>30</v>
@@ -41060,7 +41060,7 @@
         <v>3</v>
       </c>
       <c r="F1093" t="n">
-        <v>0.3519614695442604</v>
+        <v>0.3519614695442608</v>
       </c>
       <c r="G1093" t="n">
         <v>30</v>
@@ -41585,7 +41585,7 @@
         <v>3</v>
       </c>
       <c r="F1108" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1108" t="n">
         <v>30</v>
@@ -41620,7 +41620,7 @@
         <v>3</v>
       </c>
       <c r="F1109" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1109" t="n">
         <v>30</v>
@@ -41655,7 +41655,7 @@
         <v>3</v>
       </c>
       <c r="F1110" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1110" t="n">
         <v>30</v>
@@ -41690,7 +41690,7 @@
         <v>3</v>
       </c>
       <c r="F1111" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1111" t="n">
         <v>30</v>
@@ -41725,7 +41725,7 @@
         <v>3</v>
       </c>
       <c r="F1112" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1112" t="n">
         <v>30</v>
@@ -41760,7 +41760,7 @@
         <v>3</v>
       </c>
       <c r="F1113" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1113" t="n">
         <v>30</v>
@@ -41795,7 +41795,7 @@
         <v>3</v>
       </c>
       <c r="F1114" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1114" t="n">
         <v>30</v>
@@ -41830,7 +41830,7 @@
         <v>3</v>
       </c>
       <c r="F1115" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1115" t="n">
         <v>30</v>
@@ -41865,7 +41865,7 @@
         <v>3</v>
       </c>
       <c r="F1116" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1116" t="n">
         <v>30</v>
@@ -41900,7 +41900,7 @@
         <v>3</v>
       </c>
       <c r="F1117" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1117" t="n">
         <v>30</v>
@@ -41935,7 +41935,7 @@
         <v>3</v>
       </c>
       <c r="F1118" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1118" t="n">
         <v>30</v>
@@ -41970,7 +41970,7 @@
         <v>3</v>
       </c>
       <c r="F1119" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1119" t="n">
         <v>30</v>
@@ -42005,7 +42005,7 @@
         <v>3</v>
       </c>
       <c r="F1120" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1120" t="n">
         <v>30</v>
@@ -42040,7 +42040,7 @@
         <v>3</v>
       </c>
       <c r="F1121" t="n">
-        <v>0.506336281056964</v>
+        <v>0.5063362810569638</v>
       </c>
       <c r="G1121" t="n">
         <v>30</v>
@@ -42075,7 +42075,7 @@
         <v>2</v>
       </c>
       <c r="F1122" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1122" t="n">
         <v>30</v>
@@ -42110,7 +42110,7 @@
         <v>2</v>
       </c>
       <c r="F1123" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1123" t="n">
         <v>30</v>
@@ -42145,7 +42145,7 @@
         <v>2</v>
       </c>
       <c r="F1124" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1124" t="n">
         <v>30</v>
@@ -42180,7 +42180,7 @@
         <v>2</v>
       </c>
       <c r="F1125" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1125" t="n">
         <v>30</v>
@@ -42215,7 +42215,7 @@
         <v>2</v>
       </c>
       <c r="F1126" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1126" t="n">
         <v>30</v>
@@ -42250,7 +42250,7 @@
         <v>2</v>
       </c>
       <c r="F1127" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1127" t="n">
         <v>30</v>
@@ -42285,7 +42285,7 @@
         <v>2</v>
       </c>
       <c r="F1128" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1128" t="n">
         <v>30</v>
@@ -42320,7 +42320,7 @@
         <v>2</v>
       </c>
       <c r="F1129" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1129" t="n">
         <v>30</v>
@@ -42355,7 +42355,7 @@
         <v>2</v>
       </c>
       <c r="F1130" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1130" t="n">
         <v>30</v>
@@ -42390,7 +42390,7 @@
         <v>2</v>
       </c>
       <c r="F1131" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1131" t="n">
         <v>30</v>
@@ -42425,7 +42425,7 @@
         <v>2</v>
       </c>
       <c r="F1132" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1132" t="n">
         <v>30</v>
@@ -42460,7 +42460,7 @@
         <v>2</v>
       </c>
       <c r="F1133" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1133" t="n">
         <v>30</v>
@@ -42495,7 +42495,7 @@
         <v>2</v>
       </c>
       <c r="F1134" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1134" t="n">
         <v>30</v>
@@ -42530,7 +42530,7 @@
         <v>2</v>
       </c>
       <c r="F1135" t="n">
-        <v>0.2141574295685293</v>
+        <v>0.21415742956853</v>
       </c>
       <c r="G1135" t="n">
         <v>30</v>
@@ -43055,7 +43055,7 @@
         <v>2</v>
       </c>
       <c r="F1150" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1150" t="n">
         <v>30</v>
@@ -43090,7 +43090,7 @@
         <v>2</v>
       </c>
       <c r="F1151" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1151" t="n">
         <v>30</v>
@@ -43125,7 +43125,7 @@
         <v>2</v>
       </c>
       <c r="F1152" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1152" t="n">
         <v>30</v>
@@ -43160,7 +43160,7 @@
         <v>2</v>
       </c>
       <c r="F1153" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1153" t="n">
         <v>30</v>
@@ -43195,7 +43195,7 @@
         <v>2</v>
       </c>
       <c r="F1154" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1154" t="n">
         <v>30</v>
@@ -43230,7 +43230,7 @@
         <v>2</v>
       </c>
       <c r="F1155" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1155" t="n">
         <v>30</v>
@@ -43265,7 +43265,7 @@
         <v>2</v>
       </c>
       <c r="F1156" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1156" t="n">
         <v>30</v>
@@ -43300,7 +43300,7 @@
         <v>2</v>
       </c>
       <c r="F1157" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1157" t="n">
         <v>30</v>
@@ -43335,7 +43335,7 @@
         <v>2</v>
       </c>
       <c r="F1158" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1158" t="n">
         <v>30</v>
@@ -43370,7 +43370,7 @@
         <v>2</v>
       </c>
       <c r="F1159" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1159" t="n">
         <v>30</v>
@@ -43405,7 +43405,7 @@
         <v>2</v>
       </c>
       <c r="F1160" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1160" t="n">
         <v>30</v>
@@ -43440,7 +43440,7 @@
         <v>2</v>
       </c>
       <c r="F1161" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1161" t="n">
         <v>30</v>
@@ -43475,7 +43475,7 @@
         <v>2</v>
       </c>
       <c r="F1162" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1162" t="n">
         <v>30</v>
@@ -43510,7 +43510,7 @@
         <v>2</v>
       </c>
       <c r="F1163" t="n">
-        <v>0.6681232381617423</v>
+        <v>0.6681232381617428</v>
       </c>
       <c r="G1163" t="n">
         <v>30</v>
@@ -43545,7 +43545,7 @@
         <v>3</v>
       </c>
       <c r="F1164" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1164" t="n">
         <v>30</v>
@@ -43580,7 +43580,7 @@
         <v>3</v>
       </c>
       <c r="F1165" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1165" t="n">
         <v>30</v>
@@ -43615,7 +43615,7 @@
         <v>3</v>
       </c>
       <c r="F1166" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1166" t="n">
         <v>30</v>
@@ -43650,7 +43650,7 @@
         <v>3</v>
       </c>
       <c r="F1167" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1167" t="n">
         <v>30</v>
@@ -43685,7 +43685,7 @@
         <v>3</v>
       </c>
       <c r="F1168" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1168" t="n">
         <v>30</v>
@@ -43720,7 +43720,7 @@
         <v>3</v>
       </c>
       <c r="F1169" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1169" t="n">
         <v>30</v>
@@ -43755,7 +43755,7 @@
         <v>3</v>
       </c>
       <c r="F1170" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1170" t="n">
         <v>30</v>
@@ -43790,7 +43790,7 @@
         <v>3</v>
       </c>
       <c r="F1171" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1171" t="n">
         <v>30</v>
@@ -43825,7 +43825,7 @@
         <v>3</v>
       </c>
       <c r="F1172" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1172" t="n">
         <v>30</v>
@@ -43860,7 +43860,7 @@
         <v>3</v>
       </c>
       <c r="F1173" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1173" t="n">
         <v>30</v>
@@ -43895,7 +43895,7 @@
         <v>3</v>
       </c>
       <c r="F1174" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1174" t="n">
         <v>30</v>
@@ -43930,7 +43930,7 @@
         <v>3</v>
       </c>
       <c r="F1175" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1175" t="n">
         <v>30</v>
@@ -43965,7 +43965,7 @@
         <v>3</v>
       </c>
       <c r="F1176" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1176" t="n">
         <v>30</v>
@@ -44000,7 +44000,7 @@
         <v>3</v>
       </c>
       <c r="F1177" t="n">
-        <v>0.7309024331266758</v>
+        <v>0.7309024331266755</v>
       </c>
       <c r="G1177" t="n">
         <v>30</v>
@@ -45505,7 +45505,7 @@
         <v>3</v>
       </c>
       <c r="F1220" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1220" t="n">
         <v>30</v>
@@ -45540,7 +45540,7 @@
         <v>3</v>
       </c>
       <c r="F1221" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1221" t="n">
         <v>30</v>
@@ -45575,7 +45575,7 @@
         <v>3</v>
       </c>
       <c r="F1222" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1222" t="n">
         <v>30</v>
@@ -45610,7 +45610,7 @@
         <v>3</v>
       </c>
       <c r="F1223" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1223" t="n">
         <v>30</v>
@@ -45645,7 +45645,7 @@
         <v>3</v>
       </c>
       <c r="F1224" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1224" t="n">
         <v>30</v>
@@ -45680,7 +45680,7 @@
         <v>3</v>
       </c>
       <c r="F1225" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1225" t="n">
         <v>30</v>
@@ -45715,7 +45715,7 @@
         <v>3</v>
       </c>
       <c r="F1226" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1226" t="n">
         <v>30</v>
@@ -45750,7 +45750,7 @@
         <v>3</v>
       </c>
       <c r="F1227" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1227" t="n">
         <v>30</v>
@@ -45785,7 +45785,7 @@
         <v>3</v>
       </c>
       <c r="F1228" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1228" t="n">
         <v>30</v>
@@ -45820,7 +45820,7 @@
         <v>3</v>
       </c>
       <c r="F1229" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1229" t="n">
         <v>30</v>
@@ -45855,7 +45855,7 @@
         <v>3</v>
       </c>
       <c r="F1230" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1230" t="n">
         <v>30</v>
@@ -45890,7 +45890,7 @@
         <v>3</v>
       </c>
       <c r="F1231" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1231" t="n">
         <v>30</v>
@@ -45925,7 +45925,7 @@
         <v>3</v>
       </c>
       <c r="F1232" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1232" t="n">
         <v>30</v>
@@ -45960,7 +45960,7 @@
         <v>3</v>
       </c>
       <c r="F1233" t="n">
-        <v>0.6572602244687386</v>
+        <v>0.6572602244687389</v>
       </c>
       <c r="G1233" t="n">
         <v>30</v>
@@ -46572,7 +46572,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46618,7 +46618,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46664,7 +46664,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46710,7 +46710,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46756,7 +46756,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46802,7 +46802,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46848,7 +46848,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46894,7 +46894,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46940,7 +46940,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -46986,7 +46986,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47032,7 +47032,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47078,7 +47078,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47124,7 +47124,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47170,7 +47170,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47216,7 +47216,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47262,7 +47262,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47308,7 +47308,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47354,7 +47354,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47400,7 +47400,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47446,7 +47446,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47492,7 +47492,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47538,7 +47538,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47584,7 +47584,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47630,7 +47630,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47676,7 +47676,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47722,7 +47722,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47768,7 +47768,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47814,7 +47814,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47860,7 +47860,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47906,7 +47906,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47952,7 +47952,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -47998,7 +47998,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48044,7 +48044,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48090,7 +48090,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48136,7 +48136,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48182,7 +48182,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48228,7 +48228,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48274,7 +48274,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48320,7 +48320,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48366,7 +48366,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48412,7 +48412,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48458,7 +48458,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48504,7 +48504,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48550,7 +48550,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48596,7 +48596,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48642,7 +48642,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48688,7 +48688,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48734,7 +48734,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48780,7 +48780,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48826,7 +48826,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48872,7 +48872,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48918,7 +48918,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -48964,7 +48964,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49010,7 +49010,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49056,7 +49056,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49102,7 +49102,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49214,7 +49214,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49260,7 +49260,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49306,7 +49306,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49352,7 +49352,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49398,7 +49398,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49444,7 +49444,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49490,7 +49490,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49536,7 +49536,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49582,7 +49582,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49628,7 +49628,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49674,7 +49674,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49720,7 +49720,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49766,7 +49766,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49812,7 +49812,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49858,7 +49858,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49904,7 +49904,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49950,7 +49950,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -49996,7 +49996,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50042,7 +50042,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50088,7 +50088,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50134,7 +50134,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50180,7 +50180,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50226,7 +50226,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50272,7 +50272,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50318,7 +50318,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50364,7 +50364,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50410,7 +50410,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50456,7 +50456,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50502,7 +50502,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50548,7 +50548,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50594,7 +50594,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50640,7 +50640,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50686,7 +50686,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50732,7 +50732,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50778,7 +50778,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50824,7 +50824,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50870,7 +50870,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50916,7 +50916,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -50962,7 +50962,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51008,7 +51008,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51054,7 +51054,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51100,7 +51100,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51146,7 +51146,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51192,7 +51192,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51238,7 +51238,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51284,7 +51284,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51330,7 +51330,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51376,7 +51376,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51422,7 +51422,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51468,7 +51468,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51514,7 +51514,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51560,7 +51560,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51606,7 +51606,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51652,7 +51652,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51698,7 +51698,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51744,7 +51744,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
     </row>
@@ -51832,7 +51832,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00d1d8f3e63aa9a40fa4c8bc85d532d175a6f2761b3fa7d04b06814d1ca96493</t>
+          <t>7b1ba852f0405944538e558e8df7fe74468789604eb0d90372b1762be3ca036a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -51868,7 +51868,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>d5-topology-evidence-20260726</t>
+          <t>d5-topology-evidence-20260727-inventory-reverified</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>f8312bd715f08bc9d5dea8ed8434c98bfbec71ab9530ef9d8d90120e4a96e4e9</t>
+          <t>d289f2ed1790125576e6208aa59e739e900544fd5a3d6de3b66e4b01af1ed4ec</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fc246996bdcd0f15017212655ad35b72dd7d96e4eec43bcb9e5fea9f3957e8fb</t>
+          <t>c2abac4e644f6aa39140b77b7df71f2d5841d4f280544fedb43d94acbe3d2b0d</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>f0eedac9032660fbe17b8b9920fac72b186e2f9dc6b9c9405971db86a5fab765</t>
+          <t>a872e0785320e7e8f6b15fef7f2ab4d167635bf4c74ccdefaab449f03c4ad25d</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>c65b91c67204e259a7c69f7fa760ed18017143c981aa65d3d711734b7f168256</t>
+          <t>412c49bfe1e3289c79ed9039c14e4b817fd6ecd6880c7adb400eb541d2aa2afe</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0ff7bc8adfe746a36eed9918ad7dcb156931da693572c68482d72f23e425b1fd</t>
+          <t>16fb7f73931ef0bcc5044c55147e22c1e5b4d9198fc0ceaabba68e1d8236dfb8</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>eb960d8681066aa531c701f2ff8263c6fa7a91827df14cd5f802fc4f0e939cb1</t>
+          <t>7aea48aa61203adb09fa646cd3935f09c2a544db6d6ce16b1d5c15022f637b76</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>39035906df9ec1fded81b3728bc798020fc86a26ae5c1125ac53b672aec31b28</t>
+          <t>0360a1c00cfe7e0c80f9ab49d0e587dffcf9a69973e58c8f410d2fae2747272e</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>b85a30747a01feea43c0171e06a3a5e5635443a0d3fbb6480a475fb591398f2b</t>
+          <t>be3822405e2c14214629ff549e51121033850093cc454593ec5fad7937851189</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fc1f2df5573cd42cd08b5f3f3d5aab65d7481385b8dd4eb1655560849ef4d8e6</t>
+          <t>c08f738254549d88fda6d7ddf70b6e6f79fa7fd773fdf93e761fa033708d8b16</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>f6aad9dd6cfc331d694132112f20a51de8e1177c270cd4bbb7f166281963bdbd</t>
+          <t>fef0c6e7297f56553b0acb7c2441dc67bb49cb3d5d526d5bd018a27697bf51a6</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2a6543ea258e75300624e9b9e292350510aa2c351d173bbed3c3ff51569919c5</t>
+          <t>bc4a257d4b3669abeb3872eadb78119e9f2a2d2ff426028040735e84c8587139</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>412b09b568ea6bf9ea98c120a8d4810ffcc4b9c60e282d59e60a304ad64ff4aa</t>
+          <t>a9cdb0c0a34753e20cc9946ae5b75df42741d4118a2aad58006770e690fe1624</t>
         </is>
       </c>
     </row>
@@ -1476,11 +1476,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9983</v>
+        <v>9987</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>f66cad2e02e6058e23ea1544558bff89c71b6297c805d30db5ec408194382e61</t>
+          <t>78516d5fee705aee9308c5ece95ce07cb2b09aec93248e68b486446b52ecd559</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6136</v>
+        <v>6135</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>c0bf0a9d4bb4b4a04ba10325b945884fc3ff9dbe2563db65c2e85bf2f03305eb</t>
+          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72624</v>
+        <v>72619</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>a779a4aeac4c82bd4ee1f1ea1f2ba9b0fd8f079a0217ff521ac640680ffa70f2</t>
+          <t>cea6bec15bebf22e5b642e374362165e070b1a825e2c905d22c5885728698aa8</t>
         </is>
       </c>
     </row>
@@ -1626,11 +1626,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5209422</v>
+        <v>5209423</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>855000b4c1c9baeb5b01080b5c15e7cff136b3499918ebaa56035930805b5317</t>
+          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ecbeb02c2c1285846d4f9f0b88dbf278da1a0c194d46124a736a2665356893ad</t>
+          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
         </is>
       </c>
     </row>
@@ -1656,11 +1656,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>45254824</v>
+        <v>45272583</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>b46196c533474ef2a2e56b661e33def9928911b3e90ac7b6fb6e098200c88c34</t>
+          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5202013a113539fedcbf11f84847bed164f512b380c978712e8cd60767d2a8ed</t>
+          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
         </is>
       </c>
     </row>
@@ -1926,11 +1926,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28033</v>
+        <v>28036</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>b4afe3b108022b10467766365ef33146cc1991c2778350c1dc7bd2c6ad146dc4</t>
+          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
         </is>
       </c>
     </row>
@@ -1956,11 +1956,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9964</v>
+        <v>9965</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>d053b19a1d7f2a6c50f4080a33698ddaa465ad7c829d943a416bc73fd8f862dd</t>
+          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
         </is>
       </c>
     </row>
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>60791</v>
+        <v>60790</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cf67d0299512e1a849e6b4115b54905061a8ec408d060765725086af8eadeea3</t>
+          <t>3eff800b27bf69ec156f8138888d8c70af6d283d82e144d64162ae3ad416b651</t>
         </is>
       </c>
     </row>
@@ -2076,11 +2076,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7277839</v>
+        <v>7277838</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>659954b3407793180cb551f9e453f5700c00fe00e8e35d9d30156360bec78c54</t>
+          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>9a09febd2f64c3daebfbc6497f33ee99932a03ee2d99c76474870b5d8e758d3b</t>
+          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3228e392670b6b7e4cf4ae59ca73c9cc30a9f39deb7ed61d4c2b5b30148a9431</t>
+          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6b74bdce8143126cd56e229752140572345a8928aedb16d74f0f43e4a814a33f</t>
+          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>70a6002a470981c1845fdb8b6515c4c161422b921f9aafa149ece58f1fbc93fd</t>
+          <t>f627a6c9567b234ae0b9c61c2b0681a6c7a74f46d30cb9f48806c4fa7e7ca7ed</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>5dff072b15712c666dead3dd588629745b7d2556ed97f2a56253d65de236552d</t>
+          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>b39443cff99b1acc69cd752c93e0a4a56f4f86f0663715b7ba958aa9987a75bd</t>
+          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1123afd60f847e11c0bf2485aafea5afbcf5010457413fd4d30ceb7df6f4eba8</t>
+          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>f829df37d53ad5209dc4a49064a5f3b29494e00f08b1c23b8604e12280e4ef81</t>
+          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ffe2846ce2e6b715e433d9d3dee91a8226d705708caa8dee900435aa21c70647</t>
+          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
         </is>
       </c>
     </row>
@@ -2406,11 +2406,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2987622</v>
+        <v>2987712</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>592082fa5efa9958cb1d42843c7829c0472ffea2ce98c226e47077952e9ebac2</t>
+          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
         </is>
       </c>
     </row>
@@ -2421,11 +2421,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>10003889</v>
+        <v>10004039</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>e83b7c789dc587697a193958b2b6b56b5d7a3726b536f9692aaff0aa1b53a61e</t>
+          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
         </is>
       </c>
     </row>
@@ -2436,11 +2436,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>41681</v>
+        <v>41680</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>934e1de7cff35a729cedb7cc394c1586ab8448a646598fe18c94f6c61dd7c29b</t>
+          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14539</v>
+        <v>14538</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>b897bc68bcc66c202993c56c1700d80696ef344dd91d28f1709d1a3bf7a9e511</t>
+          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
         </is>
       </c>
     </row>
@@ -2481,11 +2481,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8324</v>
+        <v>8325</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>f0d0f525653abcdfe59df31be1600ad5c48cb7bc49fc7291b413add17243748d</t>
+          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>718330455f0b28a855c37e00242b9ce531f16bc9c55f3856bd9ae50c183789e9</t>
+          <t>b031365e134ba1bfee32dd92c04e35cdff1e904f78937c214e008540551a11f3</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -1104,7 +1104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19291</v>
+        <v>24952</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d289f2ed1790125576e6208aa59e739e900544fd5a3d6de3b66e4b01af1ed4ec</t>
+          <t>fc561940849ad26d15c8d38f28c15b2a69532720e790e08caf8cefe4150a7a2f</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1146,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2837</v>
+        <v>3875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>c2abac4e644f6aa39140b77b7df71f2d5841d4f280544fedb43d94acbe3d2b0d</t>
+          <t>4efe7ee048fe969fcb278e5ff2d86af60c91b20739989b3115d0903fc23cf4b6</t>
         </is>
       </c>
     </row>
@@ -1457,1048 +1457,1498 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>outputs/figures/figure_bundle_audit.json</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.pdf</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2409</v>
+        <v>55784</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>bcb82f3433cc8c9bff8b96a4bdab30af87da622e94f7769341fb0cbb80a699ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.png</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9987</v>
+        <v>638508</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>78516d5fee705aee9308c5ece95ce07cb2b09aec93248e68b486446b52ecd559</t>
+          <t>0e727c79d832125c2692a90737a1549169a2e462708c6e7ca453c71ee724c956</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.json</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.svg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>588</v>
+        <v>69107</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
+          <t>924185eb051252194293bb1f0f626a326a8fbab06ed4f94bd5482f9f20ba171d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.xlsx</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.tiff</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6135</v>
+        <v>1372644</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
+          <t>eda63abf34b431710ff6444936d9b430fec8c42fc9b6c0e4b0053d7a93527571</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>outputs/local/D5_audit_log.xlsx</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.pdf</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72619</v>
+        <v>56584</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>cea6bec15bebf22e5b642e374362165e070b1a825e2c905d22c5885728698aa8</t>
+          <t>34558954fd2e7ff1dde3e9533847ae7334f7f41df775b4848784826ec78afc9b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>outputs/local/D5_case_study_exports.xlsx</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.png</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>44198</v>
+        <v>570614</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
+          <t>c841a08eced4705db43bea80ef95f51318deed8cbc9fa59162af958206f7ec14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.svg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26857</v>
+        <v>53698</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
+          <t>d2a60d2df159dd5773262648198d95fa05aa2dfc6b36ea5ca4208c6b7b421ed5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.parquet</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.tiff</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80614</v>
+        <v>1364872</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
+          <t>deff101f038b17d4bd5a4545fd371aa0c588c56565c5238d555bfb4471899aa1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.xlsx</t>
+          <t>outputs/figures/figure_bundle_audit.json</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>140097</v>
+        <v>2409</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
+          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.parquet</t>
+          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>796803</v>
+        <v>9984</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
+          <t>f0feb1f3c9868bf39b167645436a3c13adea0cb6253ce840188905750b8c2157</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.schema.json</t>
+          <t>outputs/local/D5_admission_decision.json</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1106</v>
+        <v>588</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>215cbcde37b7836586e81e198c982e82561c42170ddda3ef2bf109052fb10e29</t>
+          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.xlsx</t>
+          <t>outputs/local/D5_admission_decision.xlsx</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5209423</v>
+        <v>6135</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
+          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.parquet</t>
+          <t>outputs/local/D5_audit_log.xlsx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7340495</v>
+        <v>74702</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
+          <t>675cf312d5aa5e97cb8f722b22af3a9782c2b91a9dd3f12f708cfd6bb4955e3c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
+          <t>outputs/local/D5_case_study_exports.xlsx</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>45272583</v>
+        <v>44198</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
+          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>outputs/local/D5_mapping_params.xlsx</t>
+          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>20237</v>
+        <v>26857</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
+          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
+          <t>outputs/local/D5_event_windows.parquet</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1060062</v>
+        <v>80614</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
+          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.parquet</t>
+          <t>outputs/local/D5_event_windows.xlsx</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>62947</v>
+        <v>140097</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
+          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.xlsx</t>
+          <t>outputs/local/D5_gate_interface.parquet</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>228952</v>
+        <v>796803</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
+          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.parquet</t>
+          <t>outputs/local/D5_gate_interface.schema.json</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3658910</v>
+        <v>1128</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
+          <t>619b0d9ef22475a5de39a752b479540987d05f9cb5d649e2f7bece38005622f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.xlsx</t>
+          <t>outputs/local/D5_gate_interface.xlsx</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>45834835</v>
+        <v>5209423</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
+          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.parquet</t>
+          <t>outputs/local/D5_main_scores_hourly.parquet</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1171194</v>
+        <v>7340495</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
+          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.schema.json</t>
+          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>834</v>
+        <v>45272583</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>e697ed5d3e9ba3b4ae628350d5592c7c5932a3326ac3721df45953d8e3569c87</t>
+          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.xlsx</t>
+          <t>outputs/local/D5_mapping_params.xlsx</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>11410677</v>
+        <v>20237</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
+          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.parquet</t>
+          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6011187</v>
+        <v>1060062</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
+          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.xlsx</t>
+          <t>outputs/local/D5_reference_window_library.parquet</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>16403976</v>
+        <v>62947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
+          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
+          <t>outputs/local/D5_reference_window_library.xlsx</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7442</v>
+        <v>228952</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
+          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.parquet</t>
+          <t>outputs/local/D5_regime_state.parquet</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6146048</v>
+        <v>3658910</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
+          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.xlsx</t>
+          <t>outputs/local/D5_regime_state.xlsx</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>15958642</v>
+        <v>45834835</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
+          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
+          <t>outputs/local/D5_report_interface.parquet</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>542571</v>
+        <v>1171194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
+          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.xlsx</t>
+          <t>outputs/local/D5_report_interface.schema.json</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>190694</v>
+        <v>853</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
+          <t>c740ff5a12c99a1a761c5f2ab45d12f5174aaac3b2201e58e6d67a1a8c87c06e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.parquet</t>
+          <t>outputs/local/D5_report_interface.xlsx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52815</v>
+        <v>11410677</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
+          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.xlsx</t>
+          <t>outputs/local/D5_sensor_influence.parquet</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28036</v>
+        <v>6011187</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
+          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
+          <t>outputs/local/D5_sensor_influence.xlsx</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>10824</v>
+        <v>16403976</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
+          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
+          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>9965</v>
+        <v>7442</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
+          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_evidence.yaml</t>
+          <t>outputs/local/D5_spatial_evidence.parquet</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2342</v>
+        <v>6146048</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
+          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.json</t>
+          <t>outputs/local/D5_spatial_evidence.xlsx</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>14821</v>
+        <v>15958642</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
+          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.schema.json</t>
+          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1263</v>
+        <v>542571</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3b6af16c6f624602a9851d780a2eb0d87f381ca851177c422c742d7fb60aed41</t>
+          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.xlsx</t>
+          <t>outputs/local/D5_spatial_templates.xlsx</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>11679</v>
+        <v>190694</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
+          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.yaml</t>
+          <t>outputs/local/D5_support_assessment.parquet</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2838</v>
+        <v>52815</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
+          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>outputs/local/D5_validation_results.xlsx</t>
+          <t>outputs/local/D5_support_assessment.xlsx</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>60790</v>
+        <v>28036</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3eff800b27bf69ec156f8138888d8c70af6d283d82e144d64162ae3ad416b651</t>
+          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.parquet</t>
+          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1618880</v>
+        <v>10824</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
+          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.xlsx</t>
+          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7277838</v>
+        <v>9965</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
+          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.csv</t>
+          <t>outputs/local/D5_topology_evidence.yaml</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>18506701</v>
+        <v>2342</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
+          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.parquet</t>
+          <t>outputs/local/D5_topology_registry.json</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>744459</v>
+        <v>14821</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
+          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
+          <t>outputs/local/D5_topology_registry.schema.json</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>519</v>
+        <v>1301</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
+          <t>0f4c6e9e6d510996d1435efd1810b4a1eaca35a989b7f3d78187e29f8ce9584e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
+          <t>outputs/local/D5_topology_registry.xlsx</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>837</v>
+        <v>11679</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>f627a6c9567b234ae0b9c61c2b0681a6c7a74f46d30cb9f48806c4fa7e7ca7ed</t>
+          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
+          <t>outputs/local/D5_topology_registry.yaml</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2047657</v>
+        <v>2838</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
+          <t>outputs/local/D5_validation_results.xlsx</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>7814</v>
+        <v>64326</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
+          <t>b4a0f5586b1108b945dba84b87a47a7f387c11fa182de0c506977f3c9870efff</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
+          <t>outputs/local/D5_zone_consensus.parquet</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2107226</v>
+        <v>1618880</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
+          <t>outputs/local/D5_zone_consensus.xlsx</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>8480</v>
+        <v>7277838</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
+          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
+          <t>outputs/plot_data/D5_plot_data.csv</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2056532</v>
+        <v>18506701</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
+          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
+          <t>outputs/plot_data/D5_plot_data.parquet</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>9043</v>
+        <v>744459</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
+          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
+          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2282</v>
+        <v>519</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
+          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
+          <t>outputs/publication/D5_coverage_strata.parquet</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2185</v>
+        <v>5837</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
+          <t>f4da589996c29b4e710131be262c3efdaa0fb822e051293f1310365aaf0e7b75</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
+          <t>outputs/publication/D5_coverage_summary.parquet</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2471</v>
+        <v>2879</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
+          <t>54201e6be7009f8ed97eb53e8abd9d8d33766757486839e1d1650d09bf1718c6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+          <t>outputs/publication/D5_d4_d5_composite.parquet</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>40336</v>
+        <v>4352</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+          <t>54eed66c77212702829f3d4bc85907babd66e415997082a0a86a8b49ea1b4556</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+          <t>outputs/publication/D5_d4_d5_dependence.parquet</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5333</v>
+        <v>4364</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
+          <t>a18b2d57e0affd0fdf036d32f43b988f92c6866b4300aa8cfa798991759f1268</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+          <t>outputs/publication/D5_decision_register.parquet</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>40363</v>
+        <v>4691</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+          <t>8c888a1b2a0a3790d1333395853deb23b7c145c3a9489c8464c595fef28427f9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+          <t>outputs/publication/D5_localization.parquet</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>5307</v>
+        <v>6980</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
+          <t>e63682e2c8a0ebeb772d9d0eae21b4be654b370f853eb939376249c595ddfcff</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+          <t>outputs/publication/D5_monthly_coverage.parquet</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>40364</v>
+        <v>6919</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+          <t>51e4fd571650b85d5e4d8c2aab7c0ca543cb81aff01517a7efacc70c08bea506</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+          <t>outputs/publication/D5_outer_refit_deltas.parquet</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>5459</v>
+        <v>7921</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+          <t>1601955bc59dfd0da87cd33e695f16ac974ad0be8ecacbdb23dfe465599ce7bf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+          <t>outputs/publication/D5_outer_refit_summary.parquet</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2409</v>
+        <v>6681</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>9ea7de7e9e34e2bc3b5c657dd72bded594918e0310ad7e231a2610ef45253f30</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+          <t>outputs/publication/D5_publication_audit_manifest.json</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2345</v>
+        <v>4364</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+          <t>e3fb4bafbf07c9310f2c5afae1737d00b609f7d8c0f563b1d51366aab2cd3df3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+          <t>outputs/publication/D5_publication_audit_tables.xlsx</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2987712</v>
+        <v>23665</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+          <t>f804b0704ef36c432f26f3faf80d6ad7cbf93f014ec02a34916644a509ae3dae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.0.md</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>10004039</v>
+        <v>5709</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+          <t>951b14afceb659a941306c90c0763fec61bf79de8cd0d5316024059cfbdf7bdf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+          <t>outputs/publication/D5_risk_coverage.parquet</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>41680</v>
+        <v>5064</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+          <t>eb0caf68ddfdc8203a64254c3aa277304432bb3fa762cb19e0b9123740a49508</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+          <t>outputs/publication/D5_support_sensitivity.parquet</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>14538</v>
+        <v>5871</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+          <t>f6ee73f3893ed53682e63122e9220948cc97ffa0c9ead47b20b6b2c739de9fda</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+          <t>outputs/publication/D5_target_influence.parquet</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9388</v>
+        <v>8536</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+          <t>77b6a0a69423e32f3f664790ccd0b4e841d967fce6370559b159ea50c758bdad</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+          <t>outputs/publication/FigD5_6_validation_coverage_source_data.xlsx</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8325</v>
+        <v>10606</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+          <t>12a62815cd1300db24c3c293d091547a95a521a3b965009db4e36ff41493ada4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>9134</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>325b0094eb3ea93567482e7648b5740f141441b830fd2e540c5805c3120d5d52</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>916</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>de2a0d79f1cc37684c35cae1e61858482c4476d9951c724a1c28dd40af6c44d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2047657</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7814</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2107226</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>8480</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2056532</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>9043</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.docx</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3111730</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>cc1e9c76ec52cffba4e49f71fddbcc746efd6c195e41cfda57373264bd57078b</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>9532</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>fc5b363eb632924c649f82b46c9848f77eff3e0f4a430ceedd119e5b7542426c</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2282</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2471</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>555abddc4fd206f1d6afe947be1fad9f7557a5162e37116fa4537fd8fcc087bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>40336</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>5333</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>40363</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5307</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>40364</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>5459</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.docx</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>40366</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3306d9a6afcb510e296a5c9031cbe916a059fb0c52e6431ad4ac8d67bf146f58</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>5670</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>f68468aa772b22e9fd44f55c62997fa53699339f963e6de09346c7a502fec34e</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2409</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2987712</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>10004039</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>41680</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>14538</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>9388</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>outputs/shadow_v2/D5_shadow_v2_manifest.json</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B123" t="n">
         <v>263</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>b031365e134ba1bfee32dd92c04e35cdff1e904f78937c214e008540551a11f3</t>
         </is>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -538,7 +538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,6 +750,36 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>SVG/PDF/600dpi PNG/TIFF and frozen plot data</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publication_artifact_hash_integrity</t>
+        </is>
+      </c>
+      <c r="B15" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>publication tables, source data and figure bundle match manifest SHA-256</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>d4_publication_dependency_current</t>
+        </is>
+      </c>
+      <c r="B16" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>exact single D4 run/calibration and main-score SHA-256; status=stale_dependency_blocked</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1131,11 +1161,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24952</v>
+        <v>28805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fc561940849ad26d15c8d38f28c15b2a69532720e790e08caf8cefe4150a7a2f</t>
+          <t>2996a12d5c57570b074196dd8036c29032857b9fde93df7aea352aa371992c38</t>
         </is>
       </c>
     </row>
@@ -1146,11 +1176,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3875</v>
+        <v>4935</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4efe7ee048fe969fcb278e5ff2d86af60c91b20739989b3115d0903fc23cf4b6</t>
+          <t>cfc1b4c9f71d05af39a974ef9463f90f52066b9e042c8f67b0930bec652f478f</t>
         </is>
       </c>
     </row>
@@ -1461,11 +1491,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>55784</v>
+        <v>54719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bcb82f3433cc8c9bff8b96a4bdab30af87da622e94f7769341fb0cbb80a699ab</t>
+          <t>ff8beec018d4d331224ef2236e7fbe172b41f929f356e23c19359572ec4fb2e3</t>
         </is>
       </c>
     </row>
@@ -1476,11 +1506,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>638508</v>
+        <v>656187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0e727c79d832125c2692a90737a1549169a2e462708c6e7ca453c71ee724c956</t>
+          <t>a5d0f89175f27a60c6eeca284615c672b5fa47f41fbbecf3c25d67ee17718553</t>
         </is>
       </c>
     </row>
@@ -1491,11 +1521,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>69107</v>
+        <v>69085</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>924185eb051252194293bb1f0f626a326a8fbab06ed4f94bd5482f9f20ba171d</t>
+          <t>60ed8eabe554b2a7c014a37929d2a8c0a6cf9253c107e31f49657ac47e37352b</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1536,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1372644</v>
+        <v>1389316</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>eda63abf34b431710ff6444936d9b430fec8c42fc9b6c0e4b0053d7a93527571</t>
+          <t>767b8e085c5fa28f4211ab49ed95097a666f52963742ae45fec71e2bfe93b160</t>
         </is>
       </c>
     </row>
@@ -1521,11 +1551,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>56584</v>
+        <v>58126</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>34558954fd2e7ff1dde3e9533847ae7334f7f41df775b4848784826ec78afc9b</t>
+          <t>1fc0731d8363ad2cc56a344a8b3410c920a9f51d34c938199548bfd4ef4d10a3</t>
         </is>
       </c>
     </row>
@@ -1536,11 +1566,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>570614</v>
+        <v>556320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>c841a08eced4705db43bea80ef95f51318deed8cbc9fa59162af958206f7ec14</t>
+          <t>f4ee30551e441baa0c19c936f58a704a215e523c88e99bdec6a4f281fc9bf8be</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1581,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53698</v>
+        <v>84804</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>d2a60d2df159dd5773262648198d95fa05aa2dfc6b36ea5ca4208c6b7b421ed5</t>
+          <t>e76ef7bdd739d477778ddbb6fc7041afcc9fc3d9b292da5b92d1bd580c195934</t>
         </is>
       </c>
     </row>
@@ -1566,1389 +1596,1569 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1364872</v>
+        <v>1186676</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>deff101f038b17d4bd5a4545fd371aa0c588c56565c5238d555bfb4471899aa1</t>
+          <t>e5e1d869d315617342e7703e07263104717240eefe21046d9d6eaee2da0a0cac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>outputs/figures/figure_bundle_audit.json</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.pdf</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2409</v>
+        <v>53301</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>49e7849bed2cbf5a3af29f9bfa72488baeb1f04a062c690e04d1a806be450f8c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.png</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9984</v>
+        <v>535313</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>f0feb1f3c9868bf39b167645436a3c13adea0cb6253ce840188905750b8c2157</t>
+          <t>25eed423cc1a6f55d00a2658d7ce4a3fd7a3e60bad1fdf6a6f6f4ff5cc3d51cb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.json</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.svg</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>588</v>
+        <v>69730</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
+          <t>9c9db61371e8dadf062ac4589057466d04d3164a6219d6ae0526685644ae2279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.xlsx</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.tiff</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>6135</v>
+        <v>1406590</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
+          <t>5e3895e9fe1ed2a5ad7e18aba0096ca11933e581e01f1cfc3cd65a08927cc045</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>outputs/local/D5_audit_log.xlsx</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.pdf</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>74702</v>
+        <v>48906</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>675cf312d5aa5e97cb8f722b22af3a9782c2b91a9dd3f12f708cfd6bb4955e3c</t>
+          <t>8967eaf6d8533c8a760b891ff04aa2f0a23251f9bbfb462bb6fddbf45c30a018</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>outputs/local/D5_case_study_exports.xlsx</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.png</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>44198</v>
+        <v>406917</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
+          <t>fd0415d6e3ed87344cc5140186fd9b86626bfd1225dfd72662dae3042f1f5360</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.svg</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26857</v>
+        <v>35150</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
+          <t>f8fdc6177a692a4ce6161c531314929cf6554203d8a30d815f015e6ec4eea8cd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.parquet</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.tiff</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80614</v>
+        <v>1040878</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
+          <t>88af281d37f8851618be048e49a8313a4a1a8a3a1e1d3f452a9b911daca6168d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.xlsx</t>
+          <t>outputs/figures/figure_bundle_audit.json</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>140097</v>
+        <v>2409</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
+          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.parquet</t>
+          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>796803</v>
+        <v>9984</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
+          <t>f0feb1f3c9868bf39b167645436a3c13adea0cb6253ce840188905750b8c2157</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.schema.json</t>
+          <t>outputs/local/D5_admission_decision.json</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1128</v>
+        <v>588</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>619b0d9ef22475a5de39a752b479540987d05f9cb5d649e2f7bece38005622f3</t>
+          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.xlsx</t>
+          <t>outputs/local/D5_admission_decision.xlsx</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5209423</v>
+        <v>6135</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
+          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.parquet</t>
+          <t>outputs/local/D5_audit_log.xlsx</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>7340495</v>
+        <v>75667</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
+          <t>e6c5af19d0fc71dd80876b444f5272a8ca648d14ee9e8fbacfb99b71178a36a7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
+          <t>outputs/local/D5_case_study_exports.xlsx</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>45272583</v>
+        <v>44198</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
+          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>outputs/local/D5_mapping_params.xlsx</t>
+          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20237</v>
+        <v>26857</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
+          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
+          <t>outputs/local/D5_event_windows.parquet</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1060062</v>
+        <v>80614</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
+          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.parquet</t>
+          <t>outputs/local/D5_event_windows.xlsx</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62947</v>
+        <v>140097</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
+          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.xlsx</t>
+          <t>outputs/local/D5_gate_interface.parquet</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>228952</v>
+        <v>796803</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
+          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.parquet</t>
+          <t>outputs/local/D5_gate_interface.schema.json</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3658910</v>
+        <v>1128</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
+          <t>619b0d9ef22475a5de39a752b479540987d05f9cb5d649e2f7bece38005622f3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.xlsx</t>
+          <t>outputs/local/D5_gate_interface.xlsx</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>45834835</v>
+        <v>5209423</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
+          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.parquet</t>
+          <t>outputs/local/D5_main_scores_hourly.parquet</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1171194</v>
+        <v>7340495</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
+          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.schema.json</t>
+          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>853</v>
+        <v>45272583</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>c740ff5a12c99a1a761c5f2ab45d12f5174aaac3b2201e58e6d67a1a8c87c06e</t>
+          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.xlsx</t>
+          <t>outputs/local/D5_mapping_params.xlsx</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>11410677</v>
+        <v>20237</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
+          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.parquet</t>
+          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>6011187</v>
+        <v>1060062</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
+          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.xlsx</t>
+          <t>outputs/local/D5_reference_window_library.parquet</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>16403976</v>
+        <v>62947</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
+          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
+          <t>outputs/local/D5_reference_window_library.xlsx</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>7442</v>
+        <v>228952</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
+          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.parquet</t>
+          <t>outputs/local/D5_regime_state.parquet</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6146048</v>
+        <v>3658910</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
+          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.xlsx</t>
+          <t>outputs/local/D5_regime_state.xlsx</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>15958642</v>
+        <v>45834835</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
+          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
+          <t>outputs/local/D5_report_interface.parquet</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>542571</v>
+        <v>1171194</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
+          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.xlsx</t>
+          <t>outputs/local/D5_report_interface.schema.json</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>190694</v>
+        <v>853</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
+          <t>c740ff5a12c99a1a761c5f2ab45d12f5174aaac3b2201e58e6d67a1a8c87c06e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.parquet</t>
+          <t>outputs/local/D5_report_interface.xlsx</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52815</v>
+        <v>11410677</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
+          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.xlsx</t>
+          <t>outputs/local/D5_sensor_influence.parquet</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28036</v>
+        <v>6011187</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
+          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
+          <t>outputs/local/D5_sensor_influence.xlsx</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>10824</v>
+        <v>16403976</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
+          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
+          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>9965</v>
+        <v>7442</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
+          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_evidence.yaml</t>
+          <t>outputs/local/D5_spatial_evidence.parquet</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2342</v>
+        <v>6146048</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
+          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.json</t>
+          <t>outputs/local/D5_spatial_evidence.xlsx</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>14821</v>
+        <v>15958642</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
+          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.schema.json</t>
+          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1301</v>
+        <v>542571</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0f4c6e9e6d510996d1435efd1810b4a1eaca35a989b7f3d78187e29f8ce9584e</t>
+          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.xlsx</t>
+          <t>outputs/local/D5_spatial_templates.xlsx</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11679</v>
+        <v>190694</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
+          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.yaml</t>
+          <t>outputs/local/D5_support_assessment.parquet</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2838</v>
+        <v>52815</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
+          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>outputs/local/D5_validation_results.xlsx</t>
+          <t>outputs/local/D5_support_assessment.xlsx</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>64326</v>
+        <v>28036</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>b4a0f5586b1108b945dba84b87a47a7f387c11fa182de0c506977f3c9870efff</t>
+          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.parquet</t>
+          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1618880</v>
+        <v>10824</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
+          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.xlsx</t>
+          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7277838</v>
+        <v>9965</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
+          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.csv</t>
+          <t>outputs/local/D5_topology_evidence.yaml</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>18506701</v>
+        <v>2342</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
+          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.parquet</t>
+          <t>outputs/local/D5_topology_registry.json</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>744459</v>
+        <v>14821</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
+          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
+          <t>outputs/local/D5_topology_registry.schema.json</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>519</v>
+        <v>1301</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
+          <t>0f4c6e9e6d510996d1435efd1810b4a1eaca35a989b7f3d78187e29f8ce9584e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_coverage_strata.parquet</t>
+          <t>outputs/local/D5_topology_registry.xlsx</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5837</v>
+        <v>11679</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>f4da589996c29b4e710131be262c3efdaa0fb822e051293f1310365aaf0e7b75</t>
+          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_coverage_summary.parquet</t>
+          <t>outputs/local/D5_topology_registry.yaml</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2879</v>
+        <v>2838</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>54201e6be7009f8ed97eb53e8abd9d8d33766757486839e1d1650d09bf1718c6</t>
+          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_d4_d5_composite.parquet</t>
+          <t>outputs/local/D5_validation_results.xlsx</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4352</v>
+        <v>64326</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>54eed66c77212702829f3d4bc85907babd66e415997082a0a86a8b49ea1b4556</t>
+          <t>b4a0f5586b1108b945dba84b87a47a7f387c11fa182de0c506977f3c9870efff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_d4_d5_dependence.parquet</t>
+          <t>outputs/local/D5_zone_consensus.parquet</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4364</v>
+        <v>1618880</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>a18b2d57e0affd0fdf036d32f43b988f92c6866b4300aa8cfa798991759f1268</t>
+          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_decision_register.parquet</t>
+          <t>outputs/local/D5_zone_consensus.xlsx</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4691</v>
+        <v>7277838</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>8c888a1b2a0a3790d1333395853deb23b7c145c3a9489c8464c595fef28427f9</t>
+          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_localization.parquet</t>
+          <t>outputs/plot_data/D5_plot_data.csv</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>6980</v>
+        <v>18506701</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>e63682e2c8a0ebeb772d9d0eae21b4be654b370f853eb939376249c595ddfcff</t>
+          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_monthly_coverage.parquet</t>
+          <t>outputs/plot_data/D5_plot_data.parquet</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>6919</v>
+        <v>744459</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>51e4fd571650b85d5e4d8c2aab7c0ca543cb81aff01517a7efacc70c08bea506</t>
+          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_outer_refit_deltas.parquet</t>
+          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>7921</v>
+        <v>519</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1601955bc59dfd0da87cd33e695f16ac974ad0be8ecacbdb23dfe465599ce7bf</t>
+          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_outer_refit_summary.parquet</t>
+          <t>outputs/publication/D5_coverage_strata.parquet</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>6681</v>
+        <v>5837</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9ea7de7e9e34e2bc3b5c657dd72bded594918e0310ad7e231a2610ef45253f30</t>
+          <t>f4da589996c29b4e710131be262c3efdaa0fb822e051293f1310365aaf0e7b75</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_publication_audit_manifest.json</t>
+          <t>outputs/publication/D5_coverage_summary.parquet</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4364</v>
+        <v>2879</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>e3fb4bafbf07c9310f2c5afae1737d00b609f7d8c0f563b1d51366aab2cd3df3</t>
+          <t>54201e6be7009f8ed97eb53e8abd9d8d33766757486839e1d1650d09bf1718c6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_publication_audit_tables.xlsx</t>
+          <t>outputs/publication/D5_d4_d5_composite.parquet</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>23665</v>
+        <v>4352</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>f804b0704ef36c432f26f3faf80d6ad7cbf93f014ec02a34916644a509ae3dae</t>
+          <t>54eed66c77212702829f3d4bc85907babd66e415997082a0a86a8b49ea1b4556</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.0.md</t>
+          <t>outputs/publication/D5_d4_d5_dependence.parquet</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>5709</v>
+        <v>5734</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>951b14afceb659a941306c90c0763fec61bf79de8cd0d5316024059cfbdf7bdf</t>
+          <t>5a460deb7c3336af77955fa2de04d3386bb208a978ec8998174b14ce2f505fa3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_risk_coverage.parquet</t>
+          <t>outputs/publication/D5_d4_d5_stratified_rho.parquet</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>5064</v>
+        <v>8751</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>eb0caf68ddfdc8203a64254c3aa277304432bb3fa762cb19e0b9123740a49508</t>
+          <t>4e274bbb6e5a161f0079a012dd37cdd2d20d7558f1b2e2ac004d56269c814ddd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_support_sensitivity.parquet</t>
+          <t>outputs/publication/D5_decision_register.parquet</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5871</v>
+        <v>4974</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>f6ee73f3893ed53682e63122e9220948cc97ffa0c9ead47b20b6b2c739de9fda</t>
+          <t>710460457bcba4163b5d64d66b94ca476495f41a95378efddd2581ffa32a0196</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_target_influence.parquet</t>
+          <t>outputs/publication/D5_dimension_availability.parquet</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>8536</v>
+        <v>12550</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>77b6a0a69423e32f3f664790ccd0b4e841d967fce6370559b159ea50c758bdad</t>
+          <t>f34750499b681fb5eefe3f811fbbec3a4d0570f45ca71a850a191b4a67c93680</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_6_validation_coverage_source_data.xlsx</t>
+          <t>outputs/publication/D5_localization.parquet</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10606</v>
+        <v>6980</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>12a62815cd1300db24c3c293d091547a95a521a3b965009db4e36ff41493ada4</t>
+          <t>e63682e2c8a0ebeb772d9d0eae21b4be654b370f853eb939376249c595ddfcff</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx</t>
+          <t>outputs/publication/D5_monthly_coverage.parquet</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>9134</v>
+        <v>6919</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>325b0094eb3ea93567482e7648b5740f141441b830fd2e540c5805c3120d5d52</t>
+          <t>51e4fd571650b85d5e4d8c2aab7c0ca543cb81aff01517a7efacc70c08bea506</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
+          <t>outputs/publication/D5_outer_refit_deltas.parquet</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>916</v>
+        <v>7921</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>de2a0d79f1cc37684c35cae1e61858482c4476d9951c724a1c28dd40af6c44d1</t>
+          <t>1601955bc59dfd0da87cd33e695f16ac974ad0be8ecacbdb23dfe465599ce7bf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
+          <t>outputs/publication/D5_outer_refit_summary.parquet</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2047657</v>
+        <v>6681</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+          <t>9ea7de7e9e34e2bc3b5c657dd72bded594918e0310ad7e231a2610ef45253f30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
+          <t>outputs/publication/D5_publication_audit_manifest.json</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>7814</v>
+        <v>10292</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
+          <t>5e18a160b4c90f186cc654abc505b2ee64abf30c70e3b7d4f659340665bb8336</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
+          <t>outputs/publication/D5_publication_audit_tables.xlsx</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2107226</v>
+        <v>30537</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+          <t>600e9aefde2898da31fc87ba4ca5d2878324ba73ec76f2b6b0d4704887c36794</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
+          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.1.md</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>8480</v>
+        <v>7400</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
+          <t>3000fd27bd303e5413d1d7eb5b5d7a464ac2e416930890be51a8a1928182ab5f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
+          <t>outputs/publication/D5_risk_coverage.parquet</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2056532</v>
+        <v>5064</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
+          <t>eb0caf68ddfdc8203a64254c3aa277304432bb3fa762cb19e0b9123740a49508</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
+          <t>outputs/publication/D5_support_sensitivity.parquet</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>9043</v>
+        <v>5871</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
+          <t>f6ee73f3893ed53682e63122e9220948cc97ffa0c9ead47b20b6b2c739de9fda</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.docx</t>
+          <t>outputs/publication/D5_target_influence.parquet</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3111730</v>
+        <v>8537</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>cc1e9c76ec52cffba4e49f71fddbcc746efd6c195e41cfda57373264bd57078b</t>
+          <t>13af4a843ab3f1942fe634e88b6bb8badd884917e8a2533d602bff89b59f54ff</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.md</t>
+          <t>outputs/publication/FigD5_6_validation_coverage_source_data.xlsx</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>9532</v>
+        <v>10606</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>fc5b363eb632924c649f82b46c9848f77eff3e0f4a430ceedd119e5b7542426c</t>
+          <t>c3a6003ecea1362dab936bfbad45fc6ef37294636555b31a7aa505186cff8080</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
+          <t>outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2282</v>
+        <v>10601</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
+          <t>8c27e8a3c215ea325839dc203b968a69582e270588e1d5bb0fca1759624c4210</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
+          <t>outputs/publication/FigD5_8_dimension_availability_sensitivity_source_data.xlsx</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2185</v>
+        <v>6490</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
+          <t>7619005d9470f6485750c452ea79fcfbff717ebab60ac2fb072170b5be2dd583</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
+          <t>outputs/publication/FigD5_9_target_support_robustness_source_data.xlsx</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2471</v>
+        <v>7501</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
+          <t>300a6cb9e7b6f8c6c8ef1f043ddea916673046772105d1209cb6d9b1dbcabf3c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.4.md</t>
+          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3600</v>
+        <v>1075</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>555abddc4fd206f1d6afe947be1fad9f7557a5162e37116fa4537fd8fcc087bb</t>
+          <t>51b1250c4db8d4e2fc5fa97b2ebe2da15e4e47b37d9de1f8097b4e24b148ad20</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>40336</v>
+        <v>2047657</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5333</v>
+        <v>7814</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
+          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>40363</v>
+        <v>2107226</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>5307</v>
+        <v>8480</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
+          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>40364</v>
+        <v>2056532</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>5459</v>
+        <v>9043</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.docx</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.docx</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>40366</v>
+        <v>3904525</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>3306d9a6afcb510e296a5c9031cbe916a059fb0c52e6431ad4ac8d67bf146f58</t>
+          <t>555acc56c3cbff9e389ab77b43e570a75b916697e57efb691387db00be069c2e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.md</t>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.md</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>5670</v>
+        <v>10252</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>f68468aa772b22e9fd44f55c62997fa53699339f963e6de09346c7a502fec34e</t>
+          <t>1bc7c85d339d3df9deb1c08eafe0aa8b0b9c7d5e81a30b9e41ef39cfa4dbbd45</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2409</v>
+        <v>2282</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2345</v>
+        <v>2185</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2987712</v>
+        <v>2471</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.4.md</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>10004039</v>
+        <v>4620</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+          <t>8eebf74993e5b086730cf83b7953f1ae363c9e94dc2eb38ec7d3475a28496094</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>41680</v>
+        <v>40336</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>14538</v>
+        <v>5333</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>9388</v>
+        <v>40363</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>8325</v>
+        <v>5307</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>40364</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>5459</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.docx</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>40394</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>87c9c02f45ee2222bed152e5932338f8c4970970af051579544d809c7118d5c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5732</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>b7d9a57e289f30d49b4a1d54acb47d2d49b883b3d55ea7113af8ec21f836baf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2409</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2987712</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>10004039</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>41680</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>14538</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>9388</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>outputs/shadow_v2/D5_shadow_v2_manifest.json</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B135" t="n">
         <v>263</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>b031365e134ba1bfee32dd92c04e35cdff1e904f78937c214e008540551a11f3</t>
         </is>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2996a12d5c57570b074196dd8036c29032857b9fde93df7aea352aa371992c38</t>
+          <t>817b400fa63e6fab3ed0b096e5dd1c4d3e5b181c912be27e6dec22582da6ad1c</t>
         </is>
       </c>
     </row>
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>75667</v>
+        <v>75669</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>e6c5af19d0fc71dd80876b444f5272a8ca648d14ee9e8fbacfb99b71178a36a7</t>
+          <t>bf0f605340ce0ce33a4bc9a3dd952bf55372ffa03a501a471da7472f9fe74554</t>
         </is>
       </c>
     </row>
@@ -2571,11 +2571,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10292</v>
+        <v>10358</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>5e18a160b4c90f186cc654abc505b2ee64abf30c70e3b7d4f659340665bb8336</t>
+          <t>a6ea3da8d8d0928abbf9557443849e45ce01a97f2d7df368fc8c8c5c3a548501</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -775,11 +775,11 @@
         </is>
       </c>
       <c r="B16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>exact single D4 run/calibration and main-score SHA-256; status=stale_dependency_blocked</t>
+          <t>exact single D4 run/calibration and main-score SHA-256; status=current</t>
         </is>
       </c>
     </row>
@@ -1161,11 +1161,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28805</v>
+        <v>28550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>817b400fa63e6fab3ed0b096e5dd1c4d3e5b181c912be27e6dec22582da6ad1c</t>
+          <t>83aa7ba54fb6d2e9499c22134ddc210a67a151f8526abb6304ba2c0c8f992802</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cfc1b4c9f71d05af39a974ef9463f90f52066b9e042c8f67b0930bec652f478f</t>
+          <t>6197278780f24a12047422d29727861d98c8487defc691e4a60bb3bb50cf9b5a</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ff8beec018d4d331224ef2236e7fbe172b41f929f356e23c19359572ec4fb2e3</t>
+          <t>bd8b424c251d78568c23fd1dee1f0804d3cd0966daca1fbd5fdbf540df016cbb</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>60ed8eabe554b2a7c014a37929d2a8c0a6cf9253c107e31f49657ac47e37352b</t>
+          <t>5b19aa268856963bd00229b76088adc9675c3a3436dcb4085c05db3c61cb0953</t>
         </is>
       </c>
     </row>
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58126</v>
+        <v>58200</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1fc0731d8363ad2cc56a344a8b3410c920a9f51d34c938199548bfd4ef4d10a3</t>
+          <t>8a1bd5a137ec759b81994ef7e9551cf10bd2c81477915a64adc2ca1831f50ff3</t>
         </is>
       </c>
     </row>
@@ -1566,11 +1566,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>556320</v>
+        <v>590625</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>f4ee30551e441baa0c19c936f58a704a215e523c88e99bdec6a4f281fc9bf8be</t>
+          <t>c3107466a7804aae1e8b6cdbc47e767cbe96c23cba16058d4c3938feb836643d</t>
         </is>
       </c>
     </row>
@@ -1581,11 +1581,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>84804</v>
+        <v>81872</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>e76ef7bdd739d477778ddbb6fc7041afcc9fc3d9b292da5b92d1bd580c195934</t>
+          <t>67662b2a2c84f2221c902cb6ff557697bd92f9a4e9292f4e526e404b56e9381d</t>
         </is>
       </c>
     </row>
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1186676</v>
+        <v>1212914</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>e5e1d869d315617342e7703e07263104717240eefe21046d9d6eaee2da0a0cac</t>
+          <t>5fe09b6465bae0438cfb3a37de8a3b0722a90a4cf39cd9831c4f2946268580e5</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>49e7849bed2cbf5a3af29f9bfa72488baeb1f04a062c690e04d1a806be450f8c</t>
+          <t>9c9d63342d1e6a526c5a27ca5fcc723e27430611f430bc4c47a67dd320b1dd5b</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9c9db61371e8dadf062ac4589057466d04d3164a6219d6ae0526685644ae2279</t>
+          <t>7bce4f67c9b29ba8abbeceea7fc611f2094ab9ebb5b9b2c1b25c515e33b723da</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8967eaf6d8533c8a760b891ff04aa2f0a23251f9bbfb462bb6fddbf45c30a018</t>
+          <t>3bfb1f572bcf662377c32482f0bab4ba428bdbae51502048b97ff6b08cd91c9f</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>f8fdc6177a692a4ce6161c531314929cf6554203d8a30d815f015e6ec4eea8cd</t>
+          <t>0fb8eba5dbe551df360f4f45870b289b41a6f6994b820a20d334b765855f5b52</t>
         </is>
       </c>
     </row>
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>75669</v>
+        <v>75667</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bf0f605340ce0ce33a4bc9a3dd952bf55372ffa03a501a471da7472f9fe74554</t>
+          <t>ed1510aad08213357a1874fb81cc5ecda662864c09f76d83047777242ec818a7</t>
         </is>
       </c>
     </row>
@@ -2436,11 +2436,11 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>4352</v>
+        <v>6628</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>54eed66c77212702829f3d4bc85907babd66e415997082a0a86a8b49ea1b4556</t>
+          <t>f6245e6b95476622c5ccdbabdd9819e0c5c449e8e2f38797f396dba21861150d</t>
         </is>
       </c>
     </row>
@@ -2451,11 +2451,11 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>5734</v>
+        <v>8012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>5a460deb7c3336af77955fa2de04d3386bb208a978ec8998174b14ce2f505fa3</t>
+          <t>f40ae7e1aaa5addf16fa4e2c943f108e37c73eac6b029232ad8d7837ed525e12</t>
         </is>
       </c>
     </row>
@@ -2466,11 +2466,11 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8751</v>
+        <v>12046</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>4e274bbb6e5a161f0079a012dd37cdd2d20d7558f1b2e2ac004d56269c814ddd</t>
+          <t>0c06b097a5a76e224113b94f072e43ee163953ea90201f9c29dcc3711c93ff58</t>
         </is>
       </c>
     </row>
@@ -2481,11 +2481,11 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4974</v>
+        <v>4954</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>710460457bcba4163b5d64d66b94ca476495f41a95378efddd2581ffa32a0196</t>
+          <t>2c82c18cd5897448165a93ce87e3423feccbe35155e74cee4d89cb6c7ad667dc</t>
         </is>
       </c>
     </row>
@@ -2571,11 +2571,11 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>10358</v>
+        <v>14709</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>a6ea3da8d8d0928abbf9557443849e45ce01a97f2d7df368fc8c8c5c3a548501</t>
+          <t>39ebf4d77c3e9e04c9a622a204f137ec2789aa8e9fed6d7ba857138eb0feb16b</t>
         </is>
       </c>
     </row>
@@ -2586,26 +2586,26 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>30537</v>
+        <v>31653</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>600e9aefde2898da31fc87ba4ca5d2878324ba73ec76f2b6b0d4704887c36794</t>
+          <t>d60260e90fd48ffe9f5eb643639d0b94f863e9346dc922ec16b33499578dc930</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.1.md</t>
+          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.2.md</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7400</v>
+        <v>7623</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3000fd27bd303e5413d1d7eb5b5d7a464ac2e416930890be51a8a1928182ab5f</t>
+          <t>17e87ac6ee94ae2295677edb510245c808ce812f503bf29c4995e47e5b95b924</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>c3a6003ecea1362dab936bfbad45fc6ef37294636555b31a7aa505186cff8080</t>
+          <t>568846bf82c1a60ce496d7724149414ac469e6978464d9a284e5b7a4717ae6e0</t>
         </is>
       </c>
     </row>
@@ -2676,11 +2676,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>10601</v>
+        <v>11724</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>8c27e8a3c215ea325839dc203b968a69582e270588e1d5bb0fca1759624c4210</t>
+          <t>6838f382cacb25c9f1c1eff8afaebee4dccb71642e079232bed30438496ca8ca</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>7619005d9470f6485750c452ea79fcfbff717ebab60ac2fb072170b5be2dd583</t>
+          <t>1ace1bc7ebbe577865e112f1ffb4910fc9a384bcfe46e8ab2d1ff0beb8e5f746</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>300a6cb9e7b6f8c6c8ef1f043ddea916673046772105d1209cb6d9b1dbcabf3c</t>
+          <t>43dc129f8d845916e79369d3dd5c07546c375da8a8b64127945fa9c6f2f9bd8d</t>
         </is>
       </c>
     </row>
@@ -2721,11 +2721,11 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>51b1250c4db8d4e2fc5fa97b2ebe2da15e4e47b37d9de1f8097b4e24b148ad20</t>
+          <t>53e0d073ef332fc162b7db37c204f7e803ab19e193a8adce3354f8cb59ac06aa</t>
         </is>
       </c>
     </row>
@@ -2826,11 +2826,11 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3904525</v>
+        <v>3942265</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>555acc56c3cbff9e389ab77b43e570a75b916697e57efb691387db00be069c2e</t>
+          <t>be2dedbef7c560882c3cb5a89778b001e9428c2003f987ed1dfb20dd1a9da3b4</t>
         </is>
       </c>
     </row>
@@ -2841,11 +2841,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10252</v>
+        <v>10364</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1bc7c85d339d3df9deb1c08eafe0aa8b0b9c7d5e81a30b9e41ef39cfa4dbbd45</t>
+          <t>159d6a0c126fa64bc59844f3deeb4494baab692d9a7d559f35cfa6ba94957c80</t>
         </is>
       </c>
     </row>
@@ -2901,11 +2901,11 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4620</v>
+        <v>4538</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>8eebf74993e5b086730cf83b7953f1ae363c9e94dc2eb38ec7d3475a28496094</t>
+          <t>3bab49b975e41041916bbf003bedcaf390c7752a5418272d83e265867375eafc</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>87c9c02f45ee2222bed152e5932338f8c4970970af051579544d809c7118d5c8</t>
+          <t>1072270e8cf7d3efdddc267aa49b1cd19f52b934979bb7b55636ac06fd50eec8</t>
         </is>
       </c>
     </row>
@@ -3021,11 +3021,11 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5732</v>
+        <v>5736</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>b7d9a57e289f30d49b4a1d54acb47d2d49b883b3d55ea7113af8ec21f836baf1</t>
+          <t>c1f9a23a8393c682257095dfa31c53a07256a104a52ccf89d1b83140d1246590</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
+++ b/Project 1 Data Quality Assessment/D5 Topological Role Consistency and Structural Representativeness/outputs/local/D5_audit_log.xlsx
@@ -1134,7 +1134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,2008 +1157,2593 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>outputs/D5_RELEASE_QA.json</t>
+          <t>outputs/audit/support_migration/01_monthly_regime_occupancy.csv</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28550</v>
+        <v>924</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>83aa7ba54fb6d2e9499c22134ddc210a67a151f8526abb6304ba2c0c8f992802</t>
+          <t>5347d963da5444a0be5bea88b976dda6fe876d709e0fc1a28c87b2ba0295173a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>outputs/figures/D5_figure_qa.json</t>
+          <t>outputs/audit/support_migration/01_monthly_regime_occupancy.parquet</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4935</v>
+        <v>5140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6197278780f24a12047422d29727861d98c8487defc691e4a60bb3bb50cf9b5a</t>
+          <t>0340167605fa9c9d10475d50763f838a712497cca690444afb0bb71e226a2ffe</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_1_framework.pdf</t>
+          <t>outputs/audit/support_migration/01b_pre_post_regime_shift.csv</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51075</v>
+        <v>466</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a872e0785320e7e8f6b15fef7f2ab4d167635bf4c74ccdefaab449f03c4ad25d</t>
+          <t>2473e9ea06589bc98d62288ccf065ec7ca6029c6131a8c3abfc861bc5995ccb2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_1_framework.png</t>
+          <t>outputs/audit/support_migration/01b_pre_post_regime_shift.parquet</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>401779</v>
+        <v>5720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>347e59f63f0c1cdf329f7375c27f3516c79e5068b4ea597ee43af1aa7d6e8236</t>
+          <t>4caf10426c2e69948060978bca58a2e72b59fc3f7d6605af031f5058212cceca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_1_framework.svg</t>
+          <t>outputs/audit/support_migration/02_template_occupancy_56.csv</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44204</v>
+        <v>61443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>412c49bfe1e3289c79ed9039c14e4b817fd6ecd6880c7adb400eb541d2aa2afe</t>
+          <t>fb197bde632972433adc93676c070d4cace136159060bfdfc84888b777498231</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_1_framework.tiff</t>
+          <t>outputs/audit/support_migration/02_template_occupancy_56.parquet</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>982482</v>
+        <v>59044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6c436b0badd0f3728278bf32e8e188eee38e9b0ab8122de2f6731b9e5f2a49de</t>
+          <t>9f198235c034d7b3eaa361a19c0520aabc2d03a65995a1eea7187608962c398b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_2_spatiotemporal.pdf</t>
+          <t>outputs/audit/support_migration/03_L1_to_L2_blockers.csv</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57597</v>
+        <v>19374</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16fb7f73931ef0bcc5044c55147e22c1e5b4d9198fc0ceaabba68e1d8236dfb8</t>
+          <t>723ed00365f968c964394181c4855f3b1776c6e441050b32a67cfcd200946868</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_2_spatiotemporal.png</t>
+          <t>outputs/audit/support_migration/03_L1_to_L2_blockers.parquet</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>342819</v>
+        <v>57939</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1a3693d32cb3698bf270272eaa1454fcb0cb327b09c0d4f07d2558e752bdc884</t>
+          <t>213d03732a77af47ec8b1ae4fa96b0a26c4eb0f63439a32c34ed7b6e7836eaf6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_2_spatiotemporal.svg</t>
+          <t>outputs/audit/support_migration/04_L2_to_L3_blockers.csv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59173</v>
+        <v>48740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7aea48aa61203adb09fa646cd3935f09c2a544db6d6ce16b1d5c15022f637b76</t>
+          <t>48d1d700d0905237c97f535df63247c1650c0f8f22c47b74f309b2804b2d93ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_2_spatiotemporal.tiff</t>
+          <t>outputs/audit/support_migration/04_L2_to_L3_blockers.parquet</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8197140</v>
+        <v>63522</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>453f55b4cbe5768323d20ed751a9ca0224df7ac78039010c8de90c4f107112ec</t>
+          <t>d84777bacf5580e70805956913b264ba4df5c8e6423670e2234d60f3043cd7e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_3_evidence.pdf</t>
+          <t>outputs/audit/support_migration/05_coverage_loss_attribution.csv</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54259</v>
+        <v>469</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0360a1c00cfe7e0c80f9ab49d0e587dffcf9a69973e58c8f410d2fae2747272e</t>
+          <t>714c034d5f1beb94038c13ab34be16befe802dd3afc986680e7750f77ed1a9f1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_3_evidence.png</t>
+          <t>outputs/audit/support_migration/05_coverage_loss_attribution.parquet</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>590613</v>
+        <v>6069</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>579af665f82a2b29865d392e3d74537346efbe4f2fdc7c0125cc31fd30404314</t>
+          <t>a3df615816060627339ba74926e06f98374c201a51f6e0600d2b68ee78439709</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_3_evidence.svg</t>
+          <t>outputs/audit/support_migration/06_counterfactual_coverage.csv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>64408</v>
+        <v>430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>be3822405e2c14214629ff549e51121033850093cc454593ec5fad7937851189</t>
+          <t>2931a2814daa7dbb3e3554bf71317442963bf75ac21e98643e9da7258283ddac</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_3_evidence.tiff</t>
+          <t>outputs/audit/support_migration/06_counterfactual_coverage.parquet</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1246956</v>
+        <v>4093</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ce6ddfc9adca0b09fadff514018446089063d21627cf2f4a86f76566e01ea7dd</t>
+          <t>1b404b74d113f445ba704c0b0a7b9fca7bbde2a8376b4067fd91159f680b63b7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_4_validation.pdf</t>
+          <t>outputs/audit/support_migration/07_reference_horizon_sensitivity.csv</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48538</v>
+        <v>1502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>c08f738254549d88fda6d7ddf70b6e6f79fa7fd773fdf93e761fa033708d8b16</t>
+          <t>6ea9bff9843486b209e330ff6180565947484dcb47947aa72f505eb57b1ee8d8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_4_validation.png</t>
+          <t>outputs/audit/support_migration/07_reference_horizon_sensitivity.parquet</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>539959</v>
+        <v>6627</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3783592511e27dd37446d891c95d88e70ad444942531f54820f8dbfa438f0a12</t>
+          <t>11a45e83adbb3d9fb6ee071280cb1552e8f0d38a5b15b1017d2c3f00403f60e8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_4_validation.svg</t>
+          <t>outputs/audit/support_migration/08_monthly_report_eligibility.csv</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>46632</v>
+        <v>726</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fef0c6e7297f56553b0acb7c2441dc67bb49cb3d5d526d5bd018a27697bf51a6</t>
+          <t>8b1b64145508b6c569118e9f6167a99a575c276bac01044a54f70ff18af29585</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_4_validation.tiff</t>
+          <t>outputs/audit/support_migration/08_monthly_report_eligibility.parquet</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1418876</v>
+        <v>4540</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>d42e75853c77121516bbc34a59c005fdee056bff211907a1269b4708db19a0ec</t>
+          <t>d34de153122c0c474939f269271a0265a386f7b3b592eb3a6cd6a5a3ba45207a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_5_governance.pdf</t>
+          <t>outputs/audit/support_migration/D5_support_migration_audit.xlsx</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62555</v>
+        <v>67591</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bc4a257d4b3669abeb3872eadb78119e9f2a2d2ff426028040735e84c8587139</t>
+          <t>f47c074542a0d05e3049c2655702e94f4ac32806a15a452530594698db82af7f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_5_governance.png</t>
+          <t>outputs/audit/support_migration/D5_SUPPORT_MIGRATION_AUDIT_REPORT.md</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>484038</v>
+        <v>4237</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>f931dad797efa29713ce271068677d91cda7a985b123f9539c886bb6c3ba7dc2</t>
+          <t>b91c1ad0a8b2c7cbfa9a8b1a5fbe498e8d240480bc212613288826e9862fa89d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_5_governance.svg</t>
+          <t>outputs/audit/support_migration/D5_support_migration_manifest.json</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>56460</v>
+        <v>9662</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>a9cdb0c0a34753e20cc9946ae5b75df42741d4118a2aad58006770e690fe1624</t>
+          <t>6f9c815df1932a4107adc4a02e153c2f547bb8afe0d0891b722b7e76966a6642</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_5_governance.tiff</t>
+          <t>outputs/D5_RELEASE_QA.json</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1182478</v>
+        <v>36870</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>c928a1e6e2a7517e6002c22db7c7a1f829c86a6555c6d34b2a44c3dd8ee11c82</t>
+          <t>ecdc7d0bc38ff52ecb173e583ec8d0dd64bb20cc9124d779c742d4f3010c192d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_6_validation_coverage.pdf</t>
+          <t>outputs/figures/D5_figure_qa.json</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54719</v>
+        <v>7580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bd8b424c251d78568c23fd1dee1f0804d3cd0966daca1fbd5fdbf540df016cbb</t>
+          <t>1d0c4e815827302ce0f19cc80dea5ff1028c03f19cf67f5676ad21c41e8290f3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_6_validation_coverage.png</t>
+          <t>outputs/figures/FigD5_1_framework.pdf</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>656187</v>
+        <v>51250</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>a5d0f89175f27a60c6eeca284615c672b5fa47f41fbbecf3c25d67ee17718553</t>
+          <t>700bb88943fb9810b204d6823f01eb5cf3c1bde5c143a6422b752bbd8fb80967</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_6_validation_coverage.svg</t>
+          <t>outputs/figures/FigD5_1_framework.png</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>69085</v>
+        <v>382812</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5b19aa268856963bd00229b76088adc9675c3a3436dcb4085c05db3c61cb0953</t>
+          <t>0b2446b6d9140788a1bcf9f67c0bc6935e14040a400b296a583c6db98855ff9e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_6_validation_coverage.tiff</t>
+          <t>outputs/figures/FigD5_1_framework.svg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1389316</v>
+        <v>41052</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>767b8e085c5fa28f4211ab49ed95097a666f52963742ae45fec71e2bfe93b160</t>
+          <t>81fa39166769bfbd5200878ccf5df9f293dfe03cf216bc6065b9d7375d93a5f2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_7_D4_D5_complementarity.pdf</t>
+          <t>outputs/figures/FigD5_1_framework.tiff</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>58200</v>
+        <v>1035836</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>8a1bd5a137ec759b81994ef7e9551cf10bd2c81477915a64adc2ca1831f50ff3</t>
+          <t>c0d57c017959f234eab3f20a81818ec333a340f21a04f90934ec079b5b9809ff</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_7_D4_D5_complementarity.png</t>
+          <t>outputs/figures/FigD5_2_spatiotemporal.pdf</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>590625</v>
+        <v>69945</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>c3107466a7804aae1e8b6cdbc47e767cbe96c23cba16058d4c3938feb836643d</t>
+          <t>78e495172970e229f4e43a04eaf13b5c4f38ed8657764e51181461d26b5b7579</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_7_D4_D5_complementarity.svg</t>
+          <t>outputs/figures/FigD5_2_spatiotemporal.png</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>81872</v>
+        <v>644906</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>67662b2a2c84f2221c902cb6ff557697bd92f9a4e9292f4e526e404b56e9381d</t>
+          <t>b4c93b8bcfd46f52d38c85251f2ff4e9e3451f864aa1893fa31200d3b0f46bb5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_7_D4_D5_complementarity.tiff</t>
+          <t>outputs/figures/FigD5_2_spatiotemporal.svg</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1212914</v>
+        <v>95904</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5fe09b6465bae0438cfb3a37de8a3b0722a90a4cf39cd9831c4f2946268580e5</t>
+          <t>61db4a191706f4995593331e103da9a66214d73d1e48f81b8507f8c2419ea92a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.pdf</t>
+          <t>outputs/figures/FigD5_2_spatiotemporal.tiff</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53301</v>
+        <v>6443510</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9c9d63342d1e6a526c5a27ca5fcc723e27430611f430bc4c47a67dd320b1dd5b</t>
+          <t>f52d34f934898c030d31ded59048cd5a1351565279c7a3eac1dedc0fee2dc829</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.png</t>
+          <t>outputs/figures/FigD5_3_evidence.pdf</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>535313</v>
+        <v>56040</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>25eed423cc1a6f55d00a2658d7ce4a3fd7a3e60bad1fdf6a6f6f4ff5cc3d51cb</t>
+          <t>076cda73773cad1ae77847209850e5dab91c8ce8dfc345e2365cbb3a41eb5675</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.svg</t>
+          <t>outputs/figures/FigD5_3_evidence.png</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>69730</v>
+        <v>718126</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7bce4f67c9b29ba8abbeceea7fc611f2094ab9ebb5b9b2c1b25c515e33b723da</t>
+          <t>47ceafcc44de75dfe3b6d904b6eac897c8a3a43e4e3d773aa9fda4bb8c592ceb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.tiff</t>
+          <t>outputs/figures/FigD5_3_evidence.svg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1406590</v>
+        <v>105761</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5e3895e9fe1ed2a5ad7e18aba0096ca11933e581e01f1cfc3cd65a08927cc045</t>
+          <t>c280a65995a28d1c23a954cc0a69136940c192de67dfa7a81a7bfaa98563c31f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_9_target_support_robustness.pdf</t>
+          <t>outputs/figures/FigD5_3_evidence.tiff</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48906</v>
+        <v>1825322</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3bfb1f572bcf662377c32482f0bab4ba428bdbae51502048b97ff6b08cd91c9f</t>
+          <t>7c4728a4cbe297d88840a97c3843091026e6d3a90f305932b70a560928238084</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_9_target_support_robustness.png</t>
+          <t>outputs/figures/FigD5_4_validation.pdf</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>406917</v>
+        <v>42966</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>fd0415d6e3ed87344cc5140186fd9b86626bfd1225dfd72662dae3042f1f5360</t>
+          <t>51a8b842ce5478a5017e32b80840fa9cc9d619a6306429cd6da4c2f38eee8048</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_9_target_support_robustness.svg</t>
+          <t>outputs/figures/FigD5_4_validation.png</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35150</v>
+        <v>531658</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0fb8eba5dbe551df360f4f45870b289b41a6f6994b820a20d334b765855f5b52</t>
+          <t>4dabbd36451b1fe017eda7bd18c5639d13c38b776456513befb056d730c546c5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>outputs/figures/FigD5_9_target_support_robustness.tiff</t>
+          <t>outputs/figures/FigD5_4_validation.svg</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1040878</v>
+        <v>37071</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>88af281d37f8851618be048e49a8313a4a1a8a3a1e1d3f452a9b911daca6168d</t>
+          <t>5cfbf6dc9d2a80409bbcf288da522083dec40e53fc51193e7412c4cc00fc5e5a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>outputs/figures/figure_bundle_audit.json</t>
+          <t>outputs/figures/FigD5_4_validation.tiff</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2409</v>
+        <v>1226424</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>29ae2daaa9e73c6936fc202a572a0b8dc48b0660ca2aaaf676c347667804ae53</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
+          <t>outputs/figures/FigD5_5_governance.pdf</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>9984</v>
+        <v>56106</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>f0feb1f3c9868bf39b167645436a3c13adea0cb6253ce840188905750b8c2157</t>
+          <t>0f8d01e72727cc30111b1bc34cfd648075d07dbbe40553905d20ae8c2fa57cf1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.json</t>
+          <t>outputs/figures/FigD5_5_governance.png</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>588</v>
+        <v>435410</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
+          <t>a0f780e4b66a562d250a8c8649b40d74cc722a0c43fe1a382765afdcea2c6e70</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>outputs/local/D5_admission_decision.xlsx</t>
+          <t>outputs/figures/FigD5_5_governance.svg</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6135</v>
+        <v>48485</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
+          <t>cb33105e67e0b4832b4e728ee303bdc081e6e0dfdaa18c7ee45db094003c6e6f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>outputs/local/D5_audit_log.xlsx</t>
+          <t>outputs/figures/FigD5_5_governance.tiff</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>75667</v>
+        <v>1078506</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ed1510aad08213357a1874fb81cc5ecda662864c09f76d83047777242ec818a7</t>
+          <t>7c17e2721f228a98f24acc27dd5d2623e1b127900a39f9b7b2054ab70e08fc44</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>outputs/local/D5_case_study_exports.xlsx</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.pdf</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44198</v>
+        <v>50513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
+          <t>fae69822c06d7028036c0c4a88a870226921ca8b43c71d52f7724fd5518d7ee6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.png</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26857</v>
+        <v>638938</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
+          <t>3142461a1958b6109fa039e5a77a089ee36f928bd138f9bb12a01f3cad740c63</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.parquet</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.svg</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>80614</v>
+        <v>58383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
+          <t>7d263bc9dbe719410f6fe02ff2ff2c86a8d61133ea85131a4f3031aac9c4b5f2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>outputs/local/D5_event_windows.xlsx</t>
+          <t>outputs/figures/FigD5_6_validation_coverage.tiff</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>140097</v>
+        <v>1346336</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
+          <t>f670f0c97d0cfec2fbcfcb834f5a843adb273c98dcce661631166ec9e6f0167b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.parquet</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.pdf</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>796803</v>
+        <v>59590</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
+          <t>1a86275a0c8388633a626f5b3c058c39ceb6f7701f87318bbba64882b5fe2332</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.schema.json</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.png</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1128</v>
+        <v>941070</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>619b0d9ef22475a5de39a752b479540987d05f9cb5d649e2f7bece38005622f3</t>
+          <t>390c439b2d1f72e3570a3b9fed2cf9e086a2b7c2dd574593978c7ac49fae1c50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>outputs/local/D5_gate_interface.xlsx</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.svg</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>5209423</v>
+        <v>201110</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
+          <t>49011a417bc95f4bd4a66fdac07618609b4c32e5417c26ea45ff6d6cf13df21b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.parquet</t>
+          <t>outputs/figures/FigD5_7_D4_D5_complementarity.tiff</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7340495</v>
+        <v>3106950</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
+          <t>5db501d151d430f33be6dcf747f3c339ec0fb67fdd29f5bc1ba969f237dec583</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.pdf</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>45272583</v>
+        <v>48207</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
+          <t>ec13a44b05b79bf3ba09bc2ca014db34668406e4f23edcdcf0da2d7d4da81bc0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>outputs/local/D5_mapping_params.xlsx</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.png</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>20237</v>
+        <v>507591</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
+          <t>d123ff696b47fc1ec14a9b2face98833eb5e69460a4277b9703974902284d091</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.svg</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1060062</v>
+        <v>58107</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
+          <t>d30a40b1fc0862d48826e5be2352894c388234d470613d7609060b232a48b4d3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.parquet</t>
+          <t>outputs/figures/FigD5_8_dimension_availability_sensitivity.tiff</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>62947</v>
+        <v>1322456</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
+          <t>45c025977c8dda152a05ab27d993512b7982c7f8a09fcd6cefea183a7178ed2a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>outputs/local/D5_reference_window_library.xlsx</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.pdf</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>228952</v>
+        <v>47131</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
+          <t>2e582cbfa3a4107275a4633b77b34688efc1ddab583723b55fc44b0022732506</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.parquet</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.png</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3658910</v>
+        <v>428997</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
+          <t>fddb68afe2f9776046e153e66f44530295cc60cb576349dd370c4f51e0492d5f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>outputs/local/D5_regime_state.xlsx</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.svg</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>45834835</v>
+        <v>47007</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
+          <t>33bd39117fca81cb32722cefdd673e69ce1f32c56e66ed02093b6e649b3a4ca0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.parquet</t>
+          <t>outputs/figures/FigD5_9_target_support_robustness.tiff</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1171194</v>
+        <v>1162650</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
+          <t>106f932ac54a22077b2b2fdef769d91f4348d62cfa9189d003833abdee64bef1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.schema.json</t>
+          <t>outputs/figures/figure_bundle_audit.json</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>853</v>
+        <v>2409</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>c740ff5a12c99a1a761c5f2ab45d12f5174aaac3b2201e58e6d67a1a8c87c06e</t>
+          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>outputs/local/D5_report_interface.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S1_monthly_regime_occupancy_migration.pdf</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>11410677</v>
+        <v>29778</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
+          <t>3b48fa368ee8089ca9a664d9373ad8a8f295d3cffe40c10cc393b643630a968c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.parquet</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S1_monthly_regime_occupancy_migration.png</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>6011187</v>
+        <v>195025</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
+          <t>5e1f70b1e62d83b95e3d139cd5ad98211537b31b82ca8e40ec2e9981dc9bc71d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_influence.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S1_monthly_regime_occupancy_migration.svg</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>16403976</v>
+        <v>20776</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
+          <t>1ccdbda0b661c80755bb837e8db1962f64bd3813d8fb959b128fe7778ecb1bf0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S1_monthly_regime_occupancy_migration.tiff</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>7442</v>
+        <v>1043412</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
+          <t>e958b1233a6d3bd2be00cca100cd572bc83415f7afd76b4bff099eeaf42496e8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.parquet</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S2_sensor_regime_maturity_map.pdf</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>6146048</v>
+        <v>38804</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
+          <t>2ddc6819a7fb31605ddc2e10b58788d1270f979388ae4fd8d99c39e29dda87e8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_evidence.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S2_sensor_regime_maturity_map.png</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>15958642</v>
+        <v>275575</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
+          <t>40458ba4446cf8d8313396c0930a4b00ccf884a0f9cbefa0d34fccfc061bf48d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S2_sensor_regime_maturity_map.svg</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>542571</v>
+        <v>39126</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
+          <t>a7bf01c9476fc145994131e4745f3a43b3497fd8d2841e3800cf2986af0c6e4d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>outputs/local/D5_spatial_templates.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S2_sensor_regime_maturity_map.tiff</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>190694</v>
+        <v>1392684</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
+          <t>5c6f3c5d7eb36085b5d5f21fe2169bf3e66fada3864a0701b5ae89d6671dd94f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.parquet</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S3_L1_blocker_matrix.pdf</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>52815</v>
+        <v>40167</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
+          <t>acf60514c88051c998ba51e7d798a1f66a61d681e08a7661f34ee6901ee4385b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>outputs/local/D5_support_assessment.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S3_L1_blocker_matrix.png</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28036</v>
+        <v>348233</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
+          <t>2345fbdefea8145e9381062a108efb0768849f9aa14039e98c154e9022bad8d9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S3_L1_blocker_matrix.svg</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>10824</v>
+        <v>33759</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
+          <t>e2e06ba5c1c261b5fe42909001284448ecbd85ba865001d792118cdcbec6360f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S3_L1_blocker_matrix.tiff</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>9965</v>
+        <v>1567634</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
+          <t>d9de222dae61272c2f284bc66286dee13048aeed54acd811b89d51a206535642</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_evidence.yaml</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S4_counterfactual_coverage_recovery.pdf</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2342</v>
+        <v>37933</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
+          <t>5585aaa9b1c03df4ef784a49a7b966e62edb852cdd5764c9380af9dc012aef74</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.json</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S4_counterfactual_coverage_recovery.png</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14821</v>
+        <v>226217</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
+          <t>c5f9e1f2e5bc01173f14c8a5b63a2cc48b13dbf3daf0f9f2bb02ea1b581dfb82</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.schema.json</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S4_counterfactual_coverage_recovery.svg</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1301</v>
+        <v>12664</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0f4c6e9e6d510996d1435efd1810b4a1eaca35a989b7f3d78187e29f8ce9584e</t>
+          <t>50164792453a9582ca727bc14f874a0287350f4f9c727263ffd187b87fe7957f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.xlsx</t>
+          <t>outputs/figures/supplementary/support_migration/FigD5_S4_counterfactual_coverage_recovery.tiff</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>11679</v>
+        <v>508582</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
+          <t>a0355132dc0114e57ce52efb1cce2c7a21a43dd52dd6d9f84adedb3051c3ba2b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>outputs/local/D5_topology_registry.yaml</t>
+          <t>outputs/local/D5_ablation_redundancy.xlsx</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2838</v>
+        <v>9984</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
+          <t>f0feb1f3c9868bf39b167645436a3c13adea0cb6253ce840188905750b8c2157</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>outputs/local/D5_validation_results.xlsx</t>
+          <t>outputs/local/D5_admission_decision.json</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>64326</v>
+        <v>588</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>b4a0f5586b1108b945dba84b87a47a7f387c11fa182de0c506977f3c9870efff</t>
+          <t>a9c40d2d57897245afa23202d8e7ba49245ff63b19b9427ab86d12003a4c1583</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.parquet</t>
+          <t>outputs/local/D5_admission_decision.xlsx</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1618880</v>
+        <v>6135</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
+          <t>96cce073f38f1f8e9d436722f18513ea84f6acf4ba33920ca07d1185db5767dd</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>outputs/local/D5_zone_consensus.xlsx</t>
+          <t>outputs/local/D5_audit_log.xlsx</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7277838</v>
+        <v>78456</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
+          <t>1be6c6483c163b412ced24fd772f84f673d2c14aecf3907d4f9b03ef516e9679</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.csv</t>
+          <t>outputs/local/D5_case_study_exports.xlsx</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>18506701</v>
+        <v>44198</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>f074d7394f60df5f9b874734fe644757863bf44e876dd97303344227afe065c3</t>
+          <t>060027cb3475620e45c16a5aed24ec4f94b00c01a7a3ba027a188963d7682dbc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data.parquet</t>
+          <t>outputs/local/D5_edge_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>744459</v>
+        <v>26857</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3236229f520cfa38329877aa013a7233229a77567e32c95b37a87d5fe94a5dd8</t>
+          <t>5b3bd2c7f60bb706732433cc146f79297976ea8f202150b40c281c932b3a6329</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
+          <t>outputs/local/D5_event_windows.parquet</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>519</v>
+        <v>80614</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>27ae5a05d462aab27e6a6359daaf99d931840e8b58d462da108ff3ca12dfc1ae</t>
+          <t>2874ab1d42be1723d6baabd3bd81b768d9f4b3fcf5459712e226f029f25a24fd</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_coverage_strata.parquet</t>
+          <t>outputs/local/D5_event_windows.xlsx</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5837</v>
+        <v>140097</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>f4da589996c29b4e710131be262c3efdaa0fb822e051293f1310365aaf0e7b75</t>
+          <t>97f101d88e4b67e9376735a772083ed8f1403eb700de6666b4a51314b7bc3dae</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_coverage_summary.parquet</t>
+          <t>outputs/local/D5_gate_interface.parquet</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2879</v>
+        <v>796803</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>54201e6be7009f8ed97eb53e8abd9d8d33766757486839e1d1650d09bf1718c6</t>
+          <t>22b640fa64ff95f0677bdcafea1517c192dd506fc11559efc53db49916918e0e</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_d4_d5_composite.parquet</t>
+          <t>outputs/local/D5_gate_interface.schema.json</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6628</v>
+        <v>1128</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>f6245e6b95476622c5ccdbabdd9819e0c5c449e8e2f38797f396dba21861150d</t>
+          <t>619b0d9ef22475a5de39a752b479540987d05f9cb5d649e2f7bece38005622f3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_d4_d5_dependence.parquet</t>
+          <t>outputs/local/D5_gate_interface.xlsx</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8012</v>
+        <v>5209423</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>f40ae7e1aaa5addf16fa4e2c943f108e37c73eac6b029232ad8d7837ed525e12</t>
+          <t>cc6458fcb96aa750a01b53bb7acfaceae4f832b53e68bd1840f57a8ee787b22c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_d4_d5_stratified_rho.parquet</t>
+          <t>outputs/local/D5_main_scores_hourly.parquet</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>12046</v>
+        <v>7340495</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>0c06b097a5a76e224113b94f072e43ee163953ea90201f9c29dcc3711c93ff58</t>
+          <t>64274562d7139d510dd3780dbd67bd2c2c5913908dbbec8ac7d4bcceb0418cd1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_decision_register.parquet</t>
+          <t>outputs/local/D5_main_scores_hourly.xlsx</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4954</v>
+        <v>45272583</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2c82c18cd5897448165a93ce87e3423feccbe35155e74cee4d89cb6c7ad667dc</t>
+          <t>2ae0e3dcb195bddabcb98ac87479345348da28818c565a978c56f75ff0ee19c9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_dimension_availability.parquet</t>
+          <t>outputs/local/D5_mapping_params.xlsx</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>12550</v>
+        <v>20237</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>f34750499b681fb5eefe3f811fbbec3a4d0570f45ca71a850a191b4a67c93680</t>
+          <t>30ffe256d465c57c614fcab9fa40d92fcd68a7c1f5fc78cbd8e0e0d00779b6a6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_localization.parquet</t>
+          <t>outputs/local/D5_multiscale_aggregates.xlsx</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>6980</v>
+        <v>1060062</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>e63682e2c8a0ebeb772d9d0eae21b4be654b370f853eb939376249c595ddfcff</t>
+          <t>96da07e011eecb169c1880e11e5c8656c9aa16a62434b3ad540a8b9a658a5da0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_monthly_coverage.parquet</t>
+          <t>outputs/local/D5_reference_window_library.parquet</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>6919</v>
+        <v>62947</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>51e4fd571650b85d5e4d8c2aab7c0ca543cb81aff01517a7efacc70c08bea506</t>
+          <t>b84bd8208e2e533e83c722868f022eaf87e07991f184e6d59e9411909e5360bc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_outer_refit_deltas.parquet</t>
+          <t>outputs/local/D5_reference_window_library.xlsx</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7921</v>
+        <v>228952</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1601955bc59dfd0da87cd33e695f16ac974ad0be8ecacbdb23dfe465599ce7bf</t>
+          <t>12bb084003accca5fd0e85f42191286a56a27c7016b617296cde45ff4004edf1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_outer_refit_summary.parquet</t>
+          <t>outputs/local/D5_regime_state.parquet</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6681</v>
+        <v>3658910</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>9ea7de7e9e34e2bc3b5c657dd72bded594918e0310ad7e231a2610ef45253f30</t>
+          <t>622dd0f5ed1473ae5de464e4207e51ff9470de209cadcee9b30cbac92f9392e8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_publication_audit_manifest.json</t>
+          <t>outputs/local/D5_regime_state.xlsx</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>14709</v>
+        <v>45834835</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>39ebf4d77c3e9e04c9a622a204f137ec2789aa8e9fed6d7ba857138eb0feb16b</t>
+          <t>427fe81df8b7861210e267f694058376a754fa724e0bbafe1b07208e32787485</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_publication_audit_tables.xlsx</t>
+          <t>outputs/local/D5_report_interface.parquet</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>31653</v>
+        <v>1171194</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>d60260e90fd48ffe9f5eb643639d0b94f863e9346dc922ec16b33499578dc930</t>
+          <t>f057e0a8037282fb43a71a94d7043c7bd3de2b4c8fa9865365bcf0427195dbda</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.2.md</t>
+          <t>outputs/local/D5_report_interface.schema.json</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7623</v>
+        <v>853</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>17e87ac6ee94ae2295677edb510245c808ce812f503bf29c4995e47e5b95b924</t>
+          <t>c740ff5a12c99a1a761c5f2ab45d12f5174aaac3b2201e58e6d67a1a8c87c06e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_risk_coverage.parquet</t>
+          <t>outputs/local/D5_report_interface.xlsx</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>5064</v>
+        <v>11410677</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>eb0caf68ddfdc8203a64254c3aa277304432bb3fa762cb19e0b9123740a49508</t>
+          <t>f9040450b3fb8204f2fea44f92c003d1cdc2acf900a29715ee732a8b9b450aae</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_support_sensitivity.parquet</t>
+          <t>outputs/local/D5_sensor_influence.parquet</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5871</v>
+        <v>6011187</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>f6ee73f3893ed53682e63122e9220948cc97ffa0c9ead47b20b6b2c739de9fda</t>
+          <t>a9270494760fcb4ae501abcf54c50e813ca74d6306d7fbca94d7ef1a1d1730a2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>outputs/publication/D5_target_influence.parquet</t>
+          <t>outputs/local/D5_sensor_influence.xlsx</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>8537</v>
+        <v>16403976</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>13af4a843ab3f1942fe634e88b6bb8badd884917e8a2533d602bff89b59f54ff</t>
+          <t>338920c1db9c7b1bc500fa43d92f02f6165187545a79f696771287bfd877a9a0</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_6_validation_coverage_source_data.xlsx</t>
+          <t>outputs/local/D5_sensor_profile_summary.xlsx</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>10606</v>
+        <v>7442</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>568846bf82c1a60ce496d7724149414ac469e6978464d9a284e5b7a4717ae6e0</t>
+          <t>aef38bd66378a9ae3b2c76a848f1ef4d51d504616c435440e45f99eadf9fb5a9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx</t>
+          <t>outputs/local/D5_spatial_evidence.parquet</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11724</v>
+        <v>6146048</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>6838f382cacb25c9f1c1eff8afaebee4dccb71642e079232bed30438496ca8ca</t>
+          <t>4edb2bd1af0cbdac8fc61382508099137349f67f6ce70da4ee1831848bfe3733</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_8_dimension_availability_sensitivity_source_data.xlsx</t>
+          <t>outputs/local/D5_spatial_evidence.xlsx</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>6490</v>
+        <v>15958642</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1ace1bc7ebbe577865e112f1ffb4910fc9a384bcfe46e8ab2d1ff0beb8e5f746</t>
+          <t>6e2a433bcdb115b841f269c5eb5184623502c7221234da51b8ade0377c120327</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>outputs/publication/FigD5_9_target_support_robustness_source_data.xlsx</t>
+          <t>outputs/local/D5_spatial_templates.template_bundle.json</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>7501</v>
+        <v>542571</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>43dc129f8d845916e79369d3dd5c07546c375da8a8b64127945fa9c6f2f9bd8d</t>
+          <t>704238fcb5551593e569bdb3e015f04cb710815fdeccbb8aa28ba9a0c7e59ace</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
+          <t>outputs/local/D5_spatial_templates.xlsx</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1058</v>
+        <v>190694</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>53e0d073ef332fc162b7db37c204f7e803ab19e193a8adce3354f8cb59ac06aa</t>
+          <t>6fc3291e19dd0663ccd33db897edbf39e67f54e7db7b1fa8de0648d06d82c6bc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
+          <t>outputs/local/D5_support_assessment.parquet</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2047657</v>
+        <v>52815</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+          <t>00d3ed69dc3899db48c841bb56c6664bc1832e365fd5fa5c13130b6d231e5750</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
+          <t>outputs/local/D5_support_assessment.xlsx</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>7814</v>
+        <v>28036</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
+          <t>34df65d8e4329d166c69a9bc505bb97a8397e537f323c5be392fba093827dd98</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
+          <t>outputs/local/D5_topology_drift_alerts.parquet</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2107226</v>
+        <v>10824</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+          <t>59d05a6c138fc18e295611bb0e39f469c07f6a25522ed809ea4f76ca018a908a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
+          <t>outputs/local/D5_topology_drift_alerts.xlsx</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>8480</v>
+        <v>9965</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
+          <t>7262caaddcf1713a512e6dd52157f3f0e4bee9ae2642dcaf63eed60ff9ce9a87</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
+          <t>outputs/local/D5_topology_evidence.yaml</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2056532</v>
+        <v>2342</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
+          <t>50abd276a9e6bbf26acb9a22d3a796ca63423d363a036422dc57c6bdfeb71920</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
+          <t>outputs/local/D5_topology_registry.json</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>9043</v>
+        <v>14821</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
+          <t>6efbf6722e2caecabf2d9999637d48bbb7c4d630dc3e9354982ed89d750965bc</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.docx</t>
+          <t>outputs/local/D5_topology_registry.schema.json</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3942265</v>
+        <v>1301</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>be2dedbef7c560882c3cb5a89778b001e9428c2003f987ed1dfb20dd1a9da3b4</t>
+          <t>0f4c6e9e6d510996d1435efd1810b4a1eaca35a989b7f3d78187e29f8ce9584e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.md</t>
+          <t>outputs/local/D5_topology_registry.xlsx</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10364</v>
+        <v>11679</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>159d6a0c126fa64bc59844f3deeb4494baab692d9a7d559f35cfa6ba94957c80</t>
+          <t>7aa5db4087c2346acc99d827f7c3a0bd49ce90540fb2ec8f56664c82b14e36ff</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
+          <t>outputs/local/D5_topology_registry.yaml</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2282</v>
+        <v>2838</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
+          <t>46e191549a0c768ee947bff4d98f26f38a93ecbce380ab4ff8114d2885dd29f9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
+          <t>outputs/local/D5_validation_results.xlsx</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2185</v>
+        <v>64326</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
+          <t>b4a0f5586b1108b945dba84b87a47a7f387c11fa182de0c506977f3c9870efff</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
+          <t>outputs/local/D5_zone_consensus.parquet</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2471</v>
+        <v>1618880</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
+          <t>0cb43651f4dc8c4a7f378cfe3be964a688e7df7a2ff45052f649259b415cdb8c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.4.md</t>
+          <t>outputs/local/D5_zone_consensus.xlsx</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>4538</v>
+        <v>7277838</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>3bab49b975e41041916bbf003bedcaf390c7752a5418272d83e265867375eafc</t>
+          <t>f43c5554c5a0c9f3e50e38f51bc0db270a9c819c3a00a9f3dc23ae658b7e7149</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+          <t>outputs/plot_data/D5_plot_data.csv</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>40336</v>
+        <v>19888935</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+          <t>2f64df8e3b0855664a65c9cbd2245e71fc82ffd28583668cf16f623c7fff91b4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+          <t>outputs/plot_data/D5_plot_data.parquet</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5333</v>
+        <v>711420</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
+          <t>9b5ba34ed66d3bf3466d541b2d6474860157c8905a1ae15e3cba3bc33cd2b5ad</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+          <t>outputs/plot_data/D5_plot_data_manifest.json</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>40363</v>
+        <v>519</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+          <t>abcf4000817bd11e46428d772225579a90b6f3584bff3de23ae7c760d36c0e7e</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+          <t>outputs/publication/D5_coverage_strata.parquet</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>5307</v>
+        <v>5837</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
+          <t>f4da589996c29b4e710131be262c3efdaa0fb822e051293f1310365aaf0e7b75</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+          <t>outputs/publication/D5_coverage_summary.parquet</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>40364</v>
+        <v>2879</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+          <t>54201e6be7009f8ed97eb53e8abd9d8d33766757486839e1d1650d09bf1718c6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+          <t>outputs/publication/D5_d4_d5_composite.parquet</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>5459</v>
+        <v>6628</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+          <t>f6245e6b95476622c5ccdbabdd9819e0c5c449e8e2f38797f396dba21861150d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.docx</t>
+          <t>outputs/publication/D5_d4_d5_dependence.parquet</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>40394</v>
+        <v>8012</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1072270e8cf7d3efdddc267aa49b1cd19f52b934979bb7b55636ac06fd50eec8</t>
+          <t>cc38200304298af4af8178ed2d35226ea9f75fb5608608fc83a1ee472b8d718b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.md</t>
+          <t>outputs/publication/D5_d4_d5_joint_sample.parquet</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5736</v>
+        <v>302250</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>c1f9a23a8393c682257095dfa31c53a07256a104a52ccf89d1b83140d1246590</t>
+          <t>62daa89703d04a89b478c644f0eaa52343b8f2911f7ab56cb0f061e8614270c6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+          <t>outputs/publication/D5_d4_d5_low_tail_overlap.parquet</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2409</v>
+        <v>6549</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>da3ebd141c082e91a1745abc60394a9bc5c09de0cd31ad6297aa5cafc4d49756</t>
+          <t>feb6a3dccb134f99fdb07ddc02fd5fa8e1a415c5c0a6d0ea5c60d693409212bb</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+          <t>outputs/publication/D5_d4_d5_stratified_rho.parquet</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2345</v>
+        <v>12046</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+          <t>b551d102dd73641908975d207793d15f892655b9ce719faba40f8c390cfcd961</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+          <t>outputs/publication/D5_decision_register.parquet</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2987712</v>
+        <v>4954</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+          <t>2c82c18cd5897448165a93ce87e3423feccbe35155e74cee4d89cb6c7ad667dc</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+          <t>outputs/publication/D5_dimension_availability.parquet</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>10004039</v>
+        <v>12550</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+          <t>f34750499b681fb5eefe3f811fbbec3a4d0570f45ca71a850a191b4a67c93680</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+          <t>outputs/publication/D5_localization.parquet</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>41680</v>
+        <v>6980</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+          <t>e63682e2c8a0ebeb772d9d0eae21b4be654b370f853eb939376249c595ddfcff</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+          <t>outputs/publication/D5_monthly_coverage.parquet</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>14538</v>
+        <v>6986</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+          <t>ecf86809c3c74c92e8c173d9f21652b60a02212bd7dcee24b6f44b815fe639fc</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+          <t>outputs/publication/D5_outer_refit_deltas.parquet</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9388</v>
+        <v>7921</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+          <t>1601955bc59dfd0da87cd33e695f16ac974ad0be8ecacbdb23dfe465599ce7bf</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+          <t>outputs/publication/D5_outer_refit_summary.parquet</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>8325</v>
+        <v>6681</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+          <t>9ea7de7e9e34e2bc3b5c657dd72bded594918e0310ad7e231a2610ef45253f30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>outputs/publication/D5_publication_audit_manifest.json</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>15638</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ec401c6052d3c339e95f508a24baf4b7c5f74f499518bf71e2faebf27c0f79e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>outputs/publication/D5_publication_audit_tables.xlsx</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1642024</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>8a654d3b301ba058725d5dfe490ecdc38435b413d1f72d41e88a4caeb81e8521</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>outputs/publication/D5_PUBLICATION_READINESS_AUDIT_v1.2.md</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>7623</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>17e87ac6ee94ae2295677edb510245c808ce812f503bf29c4995e47e5b95b924</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>outputs/publication/D5_risk_coverage.parquet</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>8219</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>c3293962b24ffdb787294c67a482f570bd2ea9610bd0bf2c864812ac0580d7ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>outputs/publication/D5_support_sensitivity.parquet</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>5871</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>f6ee73f3893ed53682e63122e9220948cc97ffa0c9ead47b20b6b2c739de9fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>outputs/publication/D5_target_influence.parquet</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>8537</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>13af4a843ab3f1942fe634e88b6bb8badd884917e8a2533d602bff89b59f54ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>outputs/publication/FigD5_6_validation_coverage_source_data.xlsx</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>11472</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2635ef66dc17d868bae2c37be718667dca0096d410d71ed5f788dc7af663e24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>outputs/publication/FigD5_7_D4_D5_complementarity_source_data.xlsx</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1621841</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>47c67a4b9f0c44e6035357109f900ff3c36492ce2eadb5c63bacfc12ce613877</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>outputs/publication/FigD5_8_dimension_availability_sensitivity_source_data.xlsx</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>6490</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>40461b5d043772a94853ea31193129a848492916623be61b848fb96fad0219e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>outputs/publication/FigD5_9_target_support_robustness_source_data.xlsx</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>7501</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>8919815720a6ad0517db7875398c0c6dfcc2e712e4637404d626236730cd66c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_CURRENT_RELEASE.md</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1058</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>720b831533e86a9c3206a20a75f825a28700075c85f488fce074ec8e5c1cad3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.docx</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2047657</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>8e5db363b70bd05b8584eb191b764d1d2beee31c2be738b56f44c9902c67fb04</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>7814</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>6de0e55c9c7f57f2c030d48076b3da316a94d53167e1c1e9d164031972691657</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.docx</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2107226</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>9dfbe96a145765a0e22e8452ec1a76f759ae52cd201b71694aa7c7e815fd8d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>8480</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5f9333b22a9d8dc1b40d9ac2f1f684ee851785bf1f742be406e6433cfc841cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2056532</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>19b15492f9b09b02820cf4ff0effd41c672a7dd0a99a42eef3886c732b622fe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>9043</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>93baa7ffe8d1d92abac60ce6896dd742d71410bb89c771ab5d8e73c9bc3d6b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.docx</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4646979</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>76018262af21c96aa3043999b8c1a5af9a3204af84ae3866bdbaa54cbb570765</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_EXPERT_REPORT_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>13170</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3f756be6fc359c29ce43b624a10149f8044b0f6db56e7b31579ab838eeed3225</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2282</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>dd5ca9eea1365f682a5166e6f8e11da3da1b6ce06652795ba6bd0112a5711bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2185</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4e3e50df15c243b7c789337fb51e9fe8f350c3815f05b408b6dd2f8aad9c4067</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2471</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>5aace3b407bf260ee6a54a95a25736b01d1ec2831a95823a45288d40270b532c</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_FIGURE_CAPTIONS_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>7540</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>bcd441c228bc9e1405610080b04e3b0bbae743630249f964595d99b65abd4c73</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.docx</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>40336</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>c2da3e9cca5ef0a5e83b63089e8deeb7299a7e0e7735c0b4751cd47f2fc47844</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.1.md</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>5333</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0303a5bbdc16689493eb5b3826d95bf7c23fc4405284ef7db01d13b5a1d1b045</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.docx</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>40363</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>eada32c51f435a6355dc873b748b4f894cbbc17bedfc4be6090371aa323aea5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.2.md</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>5307</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>b63d3b48b8902ad31fcbeac70f218c2c3abd2b1ee4293aff45cbc89fe16b950b</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.docx</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>40364</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>788d71134331e7d994e157cbfb511ef1f5966eb546d05ea3a77a8b2dd90c2fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.3.md</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>5459</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0308ed8c677cbbb3581e4022bbc99623af3de79cf83fc9283b160fd54cb8d503</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.docx</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>40394</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>f57e684efde41bd2ef99902ff89cd2ee20b9d927a48189303a0ac0887fb3712f</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>outputs/reports/D5_PROJECT_DIRECTORY_GUIDE_v2.4.md</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>7876</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>83b919cdef957f2b5ec1e9625343990e1c99d971b0ffdd7bdf246df9c062f2e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>outputs/reports/nature_figure_bundle_audit.json</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>7580</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>1d0c4e815827302ce0f19cc80dea5ff1028c03f19cf67f5676ad21c41e8290f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_sensitivity_manifest.json</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2345</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>71ddb925f1c43c2bb363be78cb221f6a90ed9d1bce2beb713989957efcb0b8d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.parquet</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>2987712</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>a54b95d4cada7ab1f9a1e4bd7723d29f46c9e3c19de2bcab6f52a9da161ba5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_scores.xlsx</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>10004039</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>1229f93be5258226bfbdc36daab2ceb3aa2b475485c1fa0392cc15ec148a97f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_shadow_template_shift.xlsx</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>41680</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3f68e2e6f4d6bc46aa021613f6b8ee25bb562d0798f1896ef47555b36c89fe35</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>outputs/sensitivity/D5_track_invariance.xlsx</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>14538</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>c9ed72b9a91d1fa854692c1cabf77687a652bf9723a7d405b4fbc08cf5b6c1c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.parquet</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>9388</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>f65546587bfb8c5a13efa5af7a38f57820bb3467cbd974c3bfad3c369a88f2c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>outputs/shadow_v2/D5_graph_structure_learning_shadow.xlsx</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>b5a4109a1f1e707a2bc54497df9a808bd01cf23a9094aed4a77ff885fef49653</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>outputs/shadow_v2/D5_shadow_v2_manifest.json</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B174" t="n">
         <v>263</v>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>b031365e134ba1bfee32dd92c04e35cdff1e904f78937c214e008540551a11f3</t>
         </is>
